--- a/projects/paper-01/04-extract/数据_6_数据提取表_v3_xhs.xlsx
+++ b/projects/paper-01/04-extract/数据_6_数据提取表_v3_xhs.xlsx
@@ -1490,7 +1490,11 @@
           <t>自制</t>
         </is>
       </c>
-      <c r="AD3" s="36" t="n"/>
+      <c r="AD3" s="36" t="inlineStr">
+        <is>
+          <t>实验室</t>
+        </is>
+      </c>
       <c r="AF3" s="36" t="inlineStr">
         <is>
           <t>是</t>
@@ -1578,10 +1582,14 @@
         </is>
       </c>
       <c r="BB3" s="36" t="n"/>
-      <c r="BC3" s="36" t="n"/>
+      <c r="BC3" s="36" t="inlineStr">
+        <is>
+          <t>RCT</t>
+        </is>
+      </c>
       <c r="BD3" s="40" t="inlineStr">
         <is>
-          <t>未填入</t>
+          <t>已填入</t>
         </is>
       </c>
       <c r="BE3" s="40" t="inlineStr">
@@ -1696,7 +1704,11 @@
           <t>自制(Borella protocol)</t>
         </is>
       </c>
-      <c r="AD4" s="38" t="n"/>
+      <c r="AD4" s="38" t="inlineStr">
+        <is>
+          <t>居家</t>
+        </is>
+      </c>
       <c r="AE4" t="n">
         <v>1.5</v>
       </c>
@@ -1785,10 +1797,14 @@
         </is>
       </c>
       <c r="BB4" s="38" t="n"/>
-      <c r="BC4" s="38" t="n"/>
+      <c r="BC4" s="38" t="inlineStr">
+        <is>
+          <t>RCT</t>
+        </is>
+      </c>
       <c r="BD4" s="40" t="inlineStr">
         <is>
-          <t>未填入</t>
+          <t>已填入</t>
         </is>
       </c>
       <c r="BE4" s="40" t="inlineStr">

--- a/projects/paper-01/04-extract/数据_6_数据提取表_v3_xhs.xlsx
+++ b/projects/paper-01/04-extract/数据_6_数据提取表_v3_xhs.xlsx
@@ -1923,7 +1923,11 @@
           <t>自制</t>
         </is>
       </c>
-      <c r="AD5" s="36" t="n"/>
+      <c r="AD5" s="36" t="inlineStr">
+        <is>
+          <t>实验室</t>
+        </is>
+      </c>
       <c r="AF5" s="36" t="inlineStr">
         <is>
           <t>是</t>
@@ -2011,10 +2015,14 @@
         </is>
       </c>
       <c r="BB5" s="36" t="n"/>
-      <c r="BC5" s="36" t="n"/>
+      <c r="BC5" s="36" t="inlineStr">
+        <is>
+          <t>RCT</t>
+        </is>
+      </c>
       <c r="BD5" s="40" t="inlineStr">
         <is>
-          <t>未填入</t>
+          <t>已填入</t>
         </is>
       </c>
       <c r="BE5" s="40" t="inlineStr">
@@ -2127,7 +2135,11 @@
           <t>自制</t>
         </is>
       </c>
-      <c r="AD6" s="38" t="n"/>
+      <c r="AD6" s="38" t="inlineStr">
+        <is>
+          <t>实验室</t>
+        </is>
+      </c>
       <c r="AE6" t="n">
         <v>5</v>
       </c>
@@ -2216,10 +2228,14 @@
         </is>
       </c>
       <c r="BB6" s="38" t="n"/>
-      <c r="BC6" s="38" t="n"/>
+      <c r="BC6" s="38" t="inlineStr">
+        <is>
+          <t>RCT</t>
+        </is>
+      </c>
       <c r="BD6" s="40" t="inlineStr">
         <is>
-          <t>未填入</t>
+          <t>已填入</t>
         </is>
       </c>
       <c r="BE6" s="40" t="inlineStr">
@@ -2338,7 +2354,11 @@
           <t>自制</t>
         </is>
       </c>
-      <c r="AD7" s="36" t="n"/>
+      <c r="AD7" s="36" t="inlineStr">
+        <is>
+          <t>实验室</t>
+        </is>
+      </c>
       <c r="AE7" t="n">
         <v>3.3</v>
       </c>
@@ -2433,10 +2453,14 @@
         </is>
       </c>
       <c r="BB7" s="36" t="n"/>
-      <c r="BC7" s="36" t="n"/>
+      <c r="BC7" s="36" t="inlineStr">
+        <is>
+          <t>准RCT</t>
+        </is>
+      </c>
       <c r="BD7" s="40" t="inlineStr">
         <is>
-          <t>未填入</t>
+          <t>已填入</t>
         </is>
       </c>
       <c r="BE7" s="40" t="inlineStr">

--- a/projects/paper-01/04-extract/数据_6_数据提取表_v3_xhs.xlsx
+++ b/projects/paper-01/04-extract/数据_6_数据提取表_v3_xhs.xlsx
@@ -2577,7 +2577,11 @@
           <t>自制(Borella protocol)</t>
         </is>
       </c>
-      <c r="AD8" s="38" t="n"/>
+      <c r="AD8" s="38" t="inlineStr">
+        <is>
+          <t>实验室</t>
+        </is>
+      </c>
       <c r="AE8" t="n">
         <v>1.5</v>
       </c>
@@ -2666,10 +2670,14 @@
         </is>
       </c>
       <c r="BB8" s="38" t="n"/>
-      <c r="BC8" s="38" t="n"/>
+      <c r="BC8" s="38" t="inlineStr">
+        <is>
+          <t>RCT</t>
+        </is>
+      </c>
       <c r="BD8" s="40" t="inlineStr">
         <is>
-          <t>未填入</t>
+          <t>已填入</t>
         </is>
       </c>
       <c r="BE8" s="40" t="inlineStr">
@@ -2787,7 +2795,11 @@
           <t>自制(JavaScript游戏)</t>
         </is>
       </c>
-      <c r="AD9" s="36" t="n"/>
+      <c r="AD9" s="36" t="inlineStr">
+        <is>
+          <t>实验室</t>
+        </is>
+      </c>
       <c r="AE9" t="n">
         <v>2</v>
       </c>
@@ -2884,10 +2896,14 @@
         </is>
       </c>
       <c r="BB9" s="36" t="n"/>
-      <c r="BC9" s="36" t="n"/>
+      <c r="BC9" s="36" t="inlineStr">
+        <is>
+          <t>RCT</t>
+        </is>
+      </c>
       <c r="BD9" s="40" t="inlineStr">
         <is>
-          <t>未填入</t>
+          <t>已填入</t>
         </is>
       </c>
       <c r="BE9" s="40" t="inlineStr">
@@ -3006,7 +3022,11 @@
           <t>自制(von Bastian protocol)</t>
         </is>
       </c>
-      <c r="AD10" s="38" t="n"/>
+      <c r="AD10" s="38" t="inlineStr">
+        <is>
+          <t>实验室</t>
+        </is>
+      </c>
       <c r="AE10" t="n">
         <v>5</v>
       </c>
@@ -3097,10 +3117,14 @@
         </is>
       </c>
       <c r="BB10" s="38" t="n"/>
-      <c r="BC10" s="38" t="n"/>
+      <c r="BC10" s="38" t="inlineStr">
+        <is>
+          <t>RCT</t>
+        </is>
+      </c>
       <c r="BD10" s="40" t="inlineStr">
         <is>
-          <t>未填入</t>
+          <t>已填入</t>
         </is>
       </c>
       <c r="BE10" s="40" t="inlineStr">
@@ -3221,7 +3245,11 @@
           <t>自制</t>
         </is>
       </c>
-      <c r="AD11" s="36" t="n"/>
+      <c r="AD11" s="36" t="inlineStr">
+        <is>
+          <t>实验室</t>
+        </is>
+      </c>
       <c r="AE11" t="n">
         <v>1.7</v>
       </c>
@@ -3310,10 +3338,14 @@
         </is>
       </c>
       <c r="BB11" s="36" t="n"/>
-      <c r="BC11" s="36" t="n"/>
+      <c r="BC11" s="36" t="inlineStr">
+        <is>
+          <t>RCT</t>
+        </is>
+      </c>
       <c r="BD11" s="40" t="inlineStr">
         <is>
-          <t>未填入</t>
+          <t>已填入</t>
         </is>
       </c>
       <c r="BE11" s="40" t="inlineStr">

--- a/projects/paper-01/04-extract/数据_6_数据提取表_v3_xhs.xlsx
+++ b/projects/paper-01/04-extract/数据_6_数据提取表_v3_xhs.xlsx
@@ -3464,7 +3464,11 @@
           <t>Cogmed</t>
         </is>
       </c>
-      <c r="AD12" s="38" t="n"/>
+      <c r="AD12" s="38" t="inlineStr">
+        <is>
+          <t>实验室</t>
+        </is>
+      </c>
       <c r="AE12" t="n">
         <v>5</v>
       </c>
@@ -3555,10 +3559,14 @@
         </is>
       </c>
       <c r="BB12" s="38" t="n"/>
-      <c r="BC12" s="38" t="n"/>
+      <c r="BC12" s="38" t="inlineStr">
+        <is>
+          <t>准RCT</t>
+        </is>
+      </c>
       <c r="BD12" s="40" t="inlineStr">
         <is>
-          <t>未填入</t>
+          <t>已填入</t>
         </is>
       </c>
       <c r="BE12" s="40" t="inlineStr">
@@ -3675,7 +3683,11 @@
           <t>自制</t>
         </is>
       </c>
-      <c r="AD13" s="36" t="n"/>
+      <c r="AD13" s="36" t="inlineStr">
+        <is>
+          <t>实验室</t>
+        </is>
+      </c>
       <c r="AE13" t="n">
         <v>5</v>
       </c>
@@ -3776,10 +3788,14 @@
         </is>
       </c>
       <c r="BB13" s="36" t="n"/>
-      <c r="BC13" s="36" t="n"/>
+      <c r="BC13" s="36" t="inlineStr">
+        <is>
+          <t>RCT</t>
+        </is>
+      </c>
       <c r="BD13" s="40" t="inlineStr">
         <is>
-          <t>未填入</t>
+          <t>已填入</t>
         </is>
       </c>
       <c r="BE13" s="40" t="inlineStr">
@@ -3897,7 +3913,11 @@
           <t>自制</t>
         </is>
       </c>
-      <c r="AD14" s="38" t="n"/>
+      <c r="AD14" s="38" t="inlineStr">
+        <is>
+          <t>实验室</t>
+        </is>
+      </c>
       <c r="AE14" t="n">
         <v>5</v>
       </c>
@@ -3988,10 +4008,14 @@
         </is>
       </c>
       <c r="BB14" s="38" t="n"/>
-      <c r="BC14" s="38" t="n"/>
+      <c r="BC14" s="38" t="inlineStr">
+        <is>
+          <t>RCT</t>
+        </is>
+      </c>
       <c r="BD14" s="40" t="inlineStr">
         <is>
-          <t>未填入</t>
+          <t>已填入</t>
         </is>
       </c>
       <c r="BE14" s="40" t="inlineStr">
@@ -4106,7 +4130,11 @@
           <t>自制</t>
         </is>
       </c>
-      <c r="AD15" s="36" t="n"/>
+      <c r="AD15" s="36" t="inlineStr">
+        <is>
+          <t>实验室</t>
+        </is>
+      </c>
       <c r="AE15" t="n">
         <v>4</v>
       </c>
@@ -4201,10 +4229,14 @@
         </is>
       </c>
       <c r="BB15" s="36" t="n"/>
-      <c r="BC15" s="36" t="n"/>
+      <c r="BC15" s="36" t="inlineStr">
+        <is>
+          <t>准RCT</t>
+        </is>
+      </c>
       <c r="BD15" s="40" t="inlineStr">
         <is>
-          <t>未填入</t>
+          <t>已填入</t>
         </is>
       </c>
       <c r="BE15" s="40" t="inlineStr">
@@ -4320,7 +4352,11 @@
           <t>自制(Borella protocol)</t>
         </is>
       </c>
-      <c r="AD16" s="38" t="n"/>
+      <c r="AD16" s="38" t="inlineStr">
+        <is>
+          <t>实验室</t>
+        </is>
+      </c>
       <c r="AE16" t="n">
         <v>1.5</v>
       </c>
@@ -4409,10 +4445,14 @@
         </is>
       </c>
       <c r="BB16" s="38" t="n"/>
-      <c r="BC16" s="38" t="n"/>
+      <c r="BC16" s="38" t="inlineStr">
+        <is>
+          <t>RCT</t>
+        </is>
+      </c>
       <c r="BD16" s="40" t="inlineStr">
         <is>
-          <t>未填入</t>
+          <t>已填入</t>
         </is>
       </c>
       <c r="BE16" s="40" t="inlineStr">
@@ -4533,7 +4573,11 @@
           <t>自制</t>
         </is>
       </c>
-      <c r="AD17" s="36" t="n"/>
+      <c r="AD17" s="36" t="inlineStr">
+        <is>
+          <t>实验室</t>
+        </is>
+      </c>
       <c r="AE17" t="n">
         <v>5</v>
       </c>
@@ -4624,10 +4668,14 @@
         </is>
       </c>
       <c r="BB17" s="36" t="n"/>
-      <c r="BC17" s="36" t="n"/>
+      <c r="BC17" s="36" t="inlineStr">
+        <is>
+          <t>RCT</t>
+        </is>
+      </c>
       <c r="BD17" s="40" t="inlineStr">
         <is>
-          <t>未填入</t>
+          <t>已填入</t>
         </is>
       </c>
       <c r="BE17" s="40" t="inlineStr">
@@ -4742,7 +4790,11 @@
           <t>自制</t>
         </is>
       </c>
-      <c r="AD18" s="38" t="n"/>
+      <c r="AD18" s="38" t="inlineStr">
+        <is>
+          <t>实验室</t>
+        </is>
+      </c>
       <c r="AE18" t="n">
         <v>3</v>
       </c>
@@ -4837,10 +4889,14 @@
         </is>
       </c>
       <c r="BB18" s="38" t="n"/>
-      <c r="BC18" s="38" t="n"/>
+      <c r="BC18" s="38" t="inlineStr">
+        <is>
+          <t>RCT</t>
+        </is>
+      </c>
       <c r="BD18" s="40" t="inlineStr">
         <is>
-          <t>未填入</t>
+          <t>已填入</t>
         </is>
       </c>
       <c r="BE18" s="40" t="inlineStr">
@@ -4958,7 +5014,11 @@
           <t>自制(Borella protocol)</t>
         </is>
       </c>
-      <c r="AD19" s="36" t="n"/>
+      <c r="AD19" s="36" t="inlineStr">
+        <is>
+          <t>实验室</t>
+        </is>
+      </c>
       <c r="AE19" t="n">
         <v>1.5</v>
       </c>
@@ -5047,10 +5107,14 @@
         </is>
       </c>
       <c r="BB19" s="36" t="n"/>
-      <c r="BC19" s="36" t="n"/>
+      <c r="BC19" s="36" t="inlineStr">
+        <is>
+          <t>RCT</t>
+        </is>
+      </c>
       <c r="BD19" s="40" t="inlineStr">
         <is>
-          <t>未填入</t>
+          <t>已填入</t>
         </is>
       </c>
       <c r="BE19" s="40" t="inlineStr">
@@ -5167,7 +5231,11 @@
           <t>自制</t>
         </is>
       </c>
-      <c r="AD20" s="38" t="n"/>
+      <c r="AD20" s="38" t="inlineStr">
+        <is>
+          <t>居家</t>
+        </is>
+      </c>
       <c r="AE20" t="n">
         <v>2</v>
       </c>
@@ -5258,10 +5326,14 @@
         </is>
       </c>
       <c r="BB20" s="38" t="n"/>
-      <c r="BC20" s="38" t="n"/>
+      <c r="BC20" s="38" t="inlineStr">
+        <is>
+          <t>RCT</t>
+        </is>
+      </c>
       <c r="BD20" s="40" t="inlineStr">
         <is>
-          <t>未填入</t>
+          <t>已填入</t>
         </is>
       </c>
       <c r="BE20" s="40" t="inlineStr">

--- a/projects/paper-01/04-extract/数据_6_数据提取表_v3_xhs.xlsx
+++ b/projects/paper-01/04-extract/数据_6_数据提取表_v3_xhs.xlsx
@@ -5450,7 +5450,11 @@
           <t>自制</t>
         </is>
       </c>
-      <c r="AD21" s="36" t="n"/>
+      <c r="AD21" s="36" t="inlineStr">
+        <is>
+          <t>实验室</t>
+        </is>
+      </c>
       <c r="AE21" t="n">
         <v>1</v>
       </c>
@@ -5541,10 +5545,14 @@
         </is>
       </c>
       <c r="BB21" s="36" t="n"/>
-      <c r="BC21" s="36" t="n"/>
+      <c r="BC21" s="36" t="inlineStr">
+        <is>
+          <t>RCT</t>
+        </is>
+      </c>
       <c r="BD21" s="40" t="inlineStr">
         <is>
-          <t>未填入</t>
+          <t>已填入</t>
         </is>
       </c>
       <c r="BE21" s="40" t="inlineStr">
@@ -5659,7 +5667,11 @@
           <t>自制(tablet-based)</t>
         </is>
       </c>
-      <c r="AD22" s="38" t="n"/>
+      <c r="AD22" s="38" t="inlineStr">
+        <is>
+          <t>实验室</t>
+        </is>
+      </c>
       <c r="AE22" t="n">
         <v>1.7</v>
       </c>
@@ -5754,10 +5766,14 @@
         </is>
       </c>
       <c r="BB22" s="38" t="n"/>
-      <c r="BC22" s="38" t="n"/>
+      <c r="BC22" s="38" t="inlineStr">
+        <is>
+          <t>准RCT</t>
+        </is>
+      </c>
       <c r="BD22" s="40" t="inlineStr">
         <is>
-          <t>未填入</t>
+          <t>已填入</t>
         </is>
       </c>
       <c r="BE22" s="40" t="inlineStr">
@@ -5875,7 +5891,11 @@
           <t>自制</t>
         </is>
       </c>
-      <c r="AD23" s="36" t="n"/>
+      <c r="AD23" s="36" t="inlineStr">
+        <is>
+          <t>实验室</t>
+        </is>
+      </c>
       <c r="AE23" t="n">
         <v>2</v>
       </c>
@@ -5970,10 +5990,14 @@
         </is>
       </c>
       <c r="BB23" s="36" t="n"/>
-      <c r="BC23" s="36" t="n"/>
+      <c r="BC23" s="36" t="inlineStr">
+        <is>
+          <t>RCT</t>
+        </is>
+      </c>
       <c r="BD23" s="40" t="inlineStr">
         <is>
-          <t>未填入</t>
+          <t>已填入</t>
         </is>
       </c>
       <c r="BE23" s="40" t="inlineStr">
@@ -6090,7 +6114,11 @@
           <t>自制(在线)</t>
         </is>
       </c>
-      <c r="AD24" s="38" t="n"/>
+      <c r="AD24" s="38" t="inlineStr">
+        <is>
+          <t>实验室</t>
+        </is>
+      </c>
       <c r="AE24" t="n">
         <v>2.5</v>
       </c>
@@ -6175,10 +6203,14 @@
         </is>
       </c>
       <c r="BB24" s="38" t="n"/>
-      <c r="BC24" s="38" t="n"/>
+      <c r="BC24" s="38" t="inlineStr">
+        <is>
+          <t>RCT</t>
+        </is>
+      </c>
       <c r="BD24" s="40" t="inlineStr">
         <is>
-          <t>未填入</t>
+          <t>已填入</t>
         </is>
       </c>
       <c r="BE24" s="40" t="inlineStr">
@@ -6295,7 +6327,11 @@
           <t>自制</t>
         </is>
       </c>
-      <c r="AD25" s="36" t="n"/>
+      <c r="AD25" s="36" t="inlineStr">
+        <is>
+          <t>实验室</t>
+        </is>
+      </c>
       <c r="AE25" t="n">
         <v>3</v>
       </c>
@@ -6384,10 +6420,14 @@
         </is>
       </c>
       <c r="BB25" s="36" t="n"/>
-      <c r="BC25" s="36" t="n"/>
+      <c r="BC25" s="36" t="inlineStr">
+        <is>
+          <t>RCT</t>
+        </is>
+      </c>
       <c r="BD25" s="40" t="inlineStr">
         <is>
-          <t>未填入</t>
+          <t>已填入</t>
         </is>
       </c>
       <c r="BE25" s="40" t="inlineStr">
@@ -6506,7 +6546,11 @@
           <t>自制</t>
         </is>
       </c>
-      <c r="AD26" s="38" t="n"/>
+      <c r="AD26" s="38" t="inlineStr">
+        <is>
+          <t>实验室</t>
+        </is>
+      </c>
       <c r="AE26" t="n">
         <v>3</v>
       </c>
@@ -6593,10 +6637,14 @@
         </is>
       </c>
       <c r="BB26" s="38" t="n"/>
-      <c r="BC26" s="38" t="n"/>
+      <c r="BC26" s="38" t="inlineStr">
+        <is>
+          <t>准RCT</t>
+        </is>
+      </c>
       <c r="BD26" s="40" t="inlineStr">
         <is>
-          <t>未填入</t>
+          <t>已填入</t>
         </is>
       </c>
       <c r="BE26" s="40" t="inlineStr">
@@ -6713,7 +6761,11 @@
           <t>PsychoPy自制</t>
         </is>
       </c>
-      <c r="AD27" s="36" t="n"/>
+      <c r="AD27" s="36" t="inlineStr">
+        <is>
+          <t>实验室</t>
+        </is>
+      </c>
       <c r="AE27" t="n">
         <v>3</v>
       </c>
@@ -6808,10 +6860,14 @@
         </is>
       </c>
       <c r="BB27" s="36" t="n"/>
-      <c r="BC27" s="36" t="n"/>
+      <c r="BC27" s="36" t="inlineStr">
+        <is>
+          <t>准RCT</t>
+        </is>
+      </c>
       <c r="BD27" s="40" t="inlineStr">
         <is>
-          <t>未填入</t>
+          <t>已填入</t>
         </is>
       </c>
       <c r="BE27" s="40" t="inlineStr">
@@ -6933,7 +6989,11 @@
           <t>自制(tablet)</t>
         </is>
       </c>
-      <c r="AD28" s="38" t="n"/>
+      <c r="AD28" s="38" t="inlineStr">
+        <is>
+          <t>实验室</t>
+        </is>
+      </c>
       <c r="AF28" s="38" t="inlineStr">
         <is>
           <t>是</t>
@@ -7019,10 +7079,14 @@
         </is>
       </c>
       <c r="BB28" s="38" t="n"/>
-      <c r="BC28" s="38" t="n"/>
+      <c r="BC28" s="38" t="inlineStr">
+        <is>
+          <t>RCT</t>
+        </is>
+      </c>
       <c r="BD28" s="40" t="inlineStr">
         <is>
-          <t>未填入</t>
+          <t>已填入</t>
         </is>
       </c>
       <c r="BE28" s="40" t="inlineStr">
@@ -7137,7 +7201,11 @@
           <t>自制</t>
         </is>
       </c>
-      <c r="AD29" s="36" t="n"/>
+      <c r="AD29" s="36" t="inlineStr">
+        <is>
+          <t>实验室</t>
+        </is>
+      </c>
       <c r="AF29" s="36" t="inlineStr">
         <is>
           <t>是</t>
@@ -7225,10 +7293,14 @@
         </is>
       </c>
       <c r="BB29" s="36" t="n"/>
-      <c r="BC29" s="36" t="n"/>
+      <c r="BC29" s="36" t="inlineStr">
+        <is>
+          <t>RCT</t>
+        </is>
+      </c>
       <c r="BD29" s="40" t="inlineStr">
         <is>
-          <t>未填入</t>
+          <t>已填入</t>
         </is>
       </c>
       <c r="BE29" s="40" t="inlineStr">
@@ -7341,7 +7413,11 @@
           <t>自制</t>
         </is>
       </c>
-      <c r="AD30" s="38" t="n"/>
+      <c r="AD30" s="38" t="inlineStr">
+        <is>
+          <t>实验室</t>
+        </is>
+      </c>
       <c r="AE30" t="n">
         <v>2</v>
       </c>
@@ -7436,10 +7512,14 @@
         </is>
       </c>
       <c r="BB30" s="38" t="n"/>
-      <c r="BC30" s="38" t="n"/>
+      <c r="BC30" s="38" t="inlineStr">
+        <is>
+          <t>RCT</t>
+        </is>
+      </c>
       <c r="BD30" s="40" t="inlineStr">
         <is>
-          <t>未填入</t>
+          <t>已填入</t>
         </is>
       </c>
       <c r="BE30" s="40" t="inlineStr">
@@ -7554,7 +7634,11 @@
           <t>自制</t>
         </is>
       </c>
-      <c r="AD31" s="36" t="n"/>
+      <c r="AD31" s="36" t="inlineStr">
+        <is>
+          <t>实验室</t>
+        </is>
+      </c>
       <c r="AE31" t="n">
         <v>2</v>
       </c>
@@ -7649,10 +7733,14 @@
         </is>
       </c>
       <c r="BB31" s="36" t="n"/>
-      <c r="BC31" s="36" t="n"/>
+      <c r="BC31" s="36" t="inlineStr">
+        <is>
+          <t>RCT</t>
+        </is>
+      </c>
       <c r="BD31" s="40" t="inlineStr">
         <is>
-          <t>未填入</t>
+          <t>已填入</t>
         </is>
       </c>
       <c r="BE31" s="40" t="inlineStr">
@@ -7763,7 +7851,11 @@
           <t>Maxmedica CACT</t>
         </is>
       </c>
-      <c r="AD32" s="38" t="n"/>
+      <c r="AD32" s="38" t="inlineStr">
+        <is>
+          <t>实验室</t>
+        </is>
+      </c>
       <c r="AE32" t="n">
         <v>5</v>
       </c>
@@ -7850,10 +7942,14 @@
         </is>
       </c>
       <c r="BB32" s="38" t="n"/>
-      <c r="BC32" s="38" t="n"/>
+      <c r="BC32" s="38" t="inlineStr">
+        <is>
+          <t>RCT</t>
+        </is>
+      </c>
       <c r="BD32" s="40" t="inlineStr">
         <is>
-          <t>未填入</t>
+          <t>已填入</t>
         </is>
       </c>
       <c r="BE32" s="40" t="inlineStr">
@@ -7966,7 +8062,11 @@
           <t>自制</t>
         </is>
       </c>
-      <c r="AD33" s="36" t="n"/>
+      <c r="AD33" s="36" t="inlineStr">
+        <is>
+          <t>实验室</t>
+        </is>
+      </c>
       <c r="AE33" t="n">
         <v>5</v>
       </c>
@@ -8053,10 +8153,14 @@
         </is>
       </c>
       <c r="BB33" s="36" t="n"/>
-      <c r="BC33" s="36" t="n"/>
+      <c r="BC33" s="36" t="inlineStr">
+        <is>
+          <t>RCT</t>
+        </is>
+      </c>
       <c r="BD33" s="40" t="inlineStr">
         <is>
-          <t>未填入</t>
+          <t>已填入</t>
         </is>
       </c>
       <c r="BE33" s="40" t="inlineStr">
@@ -8171,7 +8275,11 @@
           <t>自制</t>
         </is>
       </c>
-      <c r="AD34" s="38" t="n"/>
+      <c r="AD34" s="38" t="inlineStr">
+        <is>
+          <t>实验室</t>
+        </is>
+      </c>
       <c r="AE34" t="n">
         <v>1</v>
       </c>
@@ -8262,10 +8370,14 @@
         </is>
       </c>
       <c r="BB34" s="38" t="n"/>
-      <c r="BC34" s="38" t="n"/>
+      <c r="BC34" s="38" t="inlineStr">
+        <is>
+          <t>RCT</t>
+        </is>
+      </c>
       <c r="BD34" s="40" t="inlineStr">
         <is>
-          <t>未填入</t>
+          <t>已填入</t>
         </is>
       </c>
       <c r="BE34" s="40" t="inlineStr">
@@ -8380,7 +8492,11 @@
           <t>CogniFit</t>
         </is>
       </c>
-      <c r="AD35" s="36" t="n"/>
+      <c r="AD35" s="36" t="inlineStr">
+        <is>
+          <t>实验室</t>
+        </is>
+      </c>
       <c r="AE35" t="n">
         <v>3</v>
       </c>
@@ -8471,10 +8587,14 @@
         </is>
       </c>
       <c r="BB35" s="36" t="n"/>
-      <c r="BC35" s="36" t="n"/>
+      <c r="BC35" s="36" t="inlineStr">
+        <is>
+          <t>RCT</t>
+        </is>
+      </c>
       <c r="BD35" s="40" t="inlineStr">
         <is>
-          <t>未填入</t>
+          <t>已填入</t>
         </is>
       </c>
       <c r="BE35" s="40" t="inlineStr">
@@ -8587,7 +8707,11 @@
           <t>自制</t>
         </is>
       </c>
-      <c r="AD36" s="38" t="n"/>
+      <c r="AD36" s="38" t="inlineStr">
+        <is>
+          <t>实验室</t>
+        </is>
+      </c>
       <c r="AE36" t="n">
         <v>2</v>
       </c>
@@ -8682,10 +8806,14 @@
         </is>
       </c>
       <c r="BB36" s="38" t="n"/>
-      <c r="BC36" s="38" t="n"/>
+      <c r="BC36" s="38" t="inlineStr">
+        <is>
+          <t>RCT</t>
+        </is>
+      </c>
       <c r="BD36" s="40" t="inlineStr">
         <is>
-          <t>未填入</t>
+          <t>已填入</t>
         </is>
       </c>
       <c r="BE36" s="40" t="inlineStr">
@@ -8794,7 +8922,11 @@
           <t>自制（居家在线）</t>
         </is>
       </c>
-      <c r="AD37" s="36" t="n"/>
+      <c r="AD37" s="36" t="inlineStr">
+        <is>
+          <t>实验室</t>
+        </is>
+      </c>
       <c r="AE37" t="n">
         <v>2.7</v>
       </c>
@@ -8885,10 +9017,14 @@
         </is>
       </c>
       <c r="BB37" s="36" t="n"/>
-      <c r="BC37" s="36" t="n"/>
+      <c r="BC37" s="36" t="inlineStr">
+        <is>
+          <t>RCT</t>
+        </is>
+      </c>
       <c r="BD37" s="40" t="inlineStr">
         <is>
-          <t>未填入</t>
+          <t>已填入</t>
         </is>
       </c>
       <c r="BE37" s="40" t="inlineStr">
@@ -9001,7 +9137,11 @@
           <t>自制</t>
         </is>
       </c>
-      <c r="AD38" s="38" t="n"/>
+      <c r="AD38" s="38" t="inlineStr">
+        <is>
+          <t>实验室</t>
+        </is>
+      </c>
       <c r="AE38" t="n">
         <v>3</v>
       </c>
@@ -9100,10 +9240,14 @@
         </is>
       </c>
       <c r="BB38" s="38" t="n"/>
-      <c r="BC38" s="38" t="n"/>
+      <c r="BC38" s="38" t="inlineStr">
+        <is>
+          <t>RCT</t>
+        </is>
+      </c>
       <c r="BD38" s="40" t="inlineStr">
         <is>
-          <t>未填入</t>
+          <t>已填入</t>
         </is>
       </c>
       <c r="BE38" s="40" t="inlineStr">
@@ -9220,7 +9364,11 @@
           <t>自制</t>
         </is>
       </c>
-      <c r="AD39" s="36" t="n"/>
+      <c r="AD39" s="36" t="inlineStr">
+        <is>
+          <t>实验室</t>
+        </is>
+      </c>
       <c r="AF39" s="36" t="inlineStr">
         <is>
           <t>是</t>
@@ -9304,10 +9452,14 @@
         </is>
       </c>
       <c r="BB39" s="36" t="n"/>
-      <c r="BC39" s="36" t="n"/>
+      <c r="BC39" s="36" t="inlineStr">
+        <is>
+          <t>准RCT</t>
+        </is>
+      </c>
       <c r="BD39" s="40" t="inlineStr">
         <is>
-          <t>未填入</t>
+          <t>已填入</t>
         </is>
       </c>
       <c r="BE39" s="40" t="inlineStr">
@@ -9418,7 +9570,11 @@
           <t>商业脑训练app</t>
         </is>
       </c>
-      <c r="AD40" s="38" t="n"/>
+      <c r="AD40" s="38" t="inlineStr">
+        <is>
+          <t>实验室</t>
+        </is>
+      </c>
       <c r="AF40" s="38" t="inlineStr">
         <is>
           <t>是</t>
@@ -9506,10 +9662,14 @@
         </is>
       </c>
       <c r="BB40" s="38" t="n"/>
-      <c r="BC40" s="38" t="n"/>
+      <c r="BC40" s="38" t="inlineStr">
+        <is>
+          <t>RCT</t>
+        </is>
+      </c>
       <c r="BD40" s="40" t="inlineStr">
         <is>
-          <t>未填入</t>
+          <t>已填入</t>
         </is>
       </c>
       <c r="BE40" s="40" t="inlineStr">
@@ -9626,7 +9786,11 @@
           <t>Cogmed</t>
         </is>
       </c>
-      <c r="AD41" s="36" t="n"/>
+      <c r="AD41" s="36" t="inlineStr">
+        <is>
+          <t>实验室</t>
+        </is>
+      </c>
       <c r="AE41" t="n">
         <v>5</v>
       </c>
@@ -9721,10 +9885,14 @@
         </is>
       </c>
       <c r="BB41" s="36" t="n"/>
-      <c r="BC41" s="36" t="n"/>
+      <c r="BC41" s="36" t="inlineStr">
+        <is>
+          <t>RCT</t>
+        </is>
+      </c>
       <c r="BD41" s="40" t="inlineStr">
         <is>
-          <t>未填入</t>
+          <t>已填入</t>
         </is>
       </c>
       <c r="BE41" s="40" t="inlineStr">
@@ -9837,7 +10005,11 @@
           <t>自制（在线）</t>
         </is>
       </c>
-      <c r="AD42" s="38" t="n"/>
+      <c r="AD42" s="38" t="inlineStr">
+        <is>
+          <t>实验室</t>
+        </is>
+      </c>
       <c r="AE42" t="n">
         <v>2</v>
       </c>
@@ -9928,10 +10100,14 @@
         </is>
       </c>
       <c r="BB42" s="38" t="n"/>
-      <c r="BC42" s="38" t="n"/>
+      <c r="BC42" s="38" t="inlineStr">
+        <is>
+          <t>RCT</t>
+        </is>
+      </c>
       <c r="BD42" s="40" t="inlineStr">
         <is>
-          <t>未填入</t>
+          <t>已填入</t>
         </is>
       </c>
       <c r="BE42" s="40" t="inlineStr">
@@ -10042,7 +10218,11 @@
           <t>BrainGymmer</t>
         </is>
       </c>
-      <c r="AD43" s="36" t="n"/>
+      <c r="AD43" s="36" t="inlineStr">
+        <is>
+          <t>实验室</t>
+        </is>
+      </c>
       <c r="AE43" t="n">
         <v>5</v>
       </c>
@@ -10129,10 +10309,14 @@
         </is>
       </c>
       <c r="BB43" s="36" t="n"/>
-      <c r="BC43" s="36" t="n"/>
+      <c r="BC43" s="36" t="inlineStr">
+        <is>
+          <t>准RCT</t>
+        </is>
+      </c>
       <c r="BD43" s="40" t="inlineStr">
         <is>
-          <t>未填入</t>
+          <t>已填入</t>
         </is>
       </c>
       <c r="BE43" s="40" t="inlineStr">
@@ -10247,7 +10431,11 @@
           <t>自制</t>
         </is>
       </c>
-      <c r="AD44" s="38" t="n"/>
+      <c r="AD44" s="38" t="inlineStr">
+        <is>
+          <t>实验室</t>
+        </is>
+      </c>
       <c r="AE44" t="n">
         <v>2</v>
       </c>
@@ -10346,10 +10534,14 @@
         </is>
       </c>
       <c r="BB44" s="38" t="n"/>
-      <c r="BC44" s="38" t="n"/>
+      <c r="BC44" s="38" t="inlineStr">
+        <is>
+          <t>RCT</t>
+        </is>
+      </c>
       <c r="BD44" s="40" t="inlineStr">
         <is>
-          <t>未填入</t>
+          <t>已填入</t>
         </is>
       </c>
       <c r="BE44" s="40" t="inlineStr">
@@ -10460,7 +10652,11 @@
           <t>BrainGymmer</t>
         </is>
       </c>
-      <c r="AD45" s="36" t="n"/>
+      <c r="AD45" s="36" t="inlineStr">
+        <is>
+          <t>实验室</t>
+        </is>
+      </c>
       <c r="AE45" t="n">
         <v>5</v>
       </c>
@@ -10551,10 +10747,14 @@
         </is>
       </c>
       <c r="BB45" s="36" t="n"/>
-      <c r="BC45" s="36" t="n"/>
+      <c r="BC45" s="36" t="inlineStr">
+        <is>
+          <t>准RCT</t>
+        </is>
+      </c>
       <c r="BD45" s="40" t="inlineStr">
         <is>
-          <t>未填入</t>
+          <t>已填入</t>
         </is>
       </c>
       <c r="BE45" s="40" t="inlineStr">
@@ -10667,7 +10867,11 @@
           <t>自制</t>
         </is>
       </c>
-      <c r="AD46" s="38" t="n"/>
+      <c r="AD46" s="38" t="inlineStr">
+        <is>
+          <t>实验室</t>
+        </is>
+      </c>
       <c r="AE46" t="n">
         <v>5</v>
       </c>
@@ -10762,10 +10966,14 @@
         </is>
       </c>
       <c r="BB46" s="38" t="n"/>
-      <c r="BC46" s="38" t="n"/>
+      <c r="BC46" s="38" t="inlineStr">
+        <is>
+          <t>准RCT</t>
+        </is>
+      </c>
       <c r="BD46" s="40" t="inlineStr">
         <is>
-          <t>未填入</t>
+          <t>已填入</t>
         </is>
       </c>
       <c r="BE46" s="40" t="inlineStr">
@@ -10874,7 +11082,11 @@
           <t>自制</t>
         </is>
       </c>
-      <c r="AD47" s="36" t="n"/>
+      <c r="AD47" s="36" t="inlineStr">
+        <is>
+          <t>实验室</t>
+        </is>
+      </c>
       <c r="AF47" s="36" t="inlineStr">
         <is>
           <t>是</t>
@@ -10962,10 +11174,14 @@
         </is>
       </c>
       <c r="BB47" s="36" t="n"/>
-      <c r="BC47" s="36" t="n"/>
+      <c r="BC47" s="36" t="inlineStr">
+        <is>
+          <t>RCT</t>
+        </is>
+      </c>
       <c r="BD47" s="40" t="inlineStr">
         <is>
-          <t>未填入</t>
+          <t>已填入</t>
         </is>
       </c>
       <c r="BE47" s="40" t="inlineStr">
@@ -11080,7 +11296,11 @@
           <t>自制（居家）</t>
         </is>
       </c>
-      <c r="AD48" s="38" t="n"/>
+      <c r="AD48" s="38" t="inlineStr">
+        <is>
+          <t>实验室</t>
+        </is>
+      </c>
       <c r="AE48" t="n">
         <v>4</v>
       </c>
@@ -11171,10 +11391,14 @@
         </is>
       </c>
       <c r="BB48" s="38" t="n"/>
-      <c r="BC48" s="38" t="n"/>
+      <c r="BC48" s="38" t="inlineStr">
+        <is>
+          <t>RCT</t>
+        </is>
+      </c>
       <c r="BD48" s="40" t="inlineStr">
         <is>
-          <t>未填入</t>
+          <t>已填入</t>
         </is>
       </c>
       <c r="BE48" s="40" t="inlineStr">
@@ -11287,7 +11511,11 @@
           <t>自制</t>
         </is>
       </c>
-      <c r="AD49" s="36" t="n"/>
+      <c r="AD49" s="36" t="inlineStr">
+        <is>
+          <t>实验室</t>
+        </is>
+      </c>
       <c r="AE49" t="n">
         <v>2</v>
       </c>
@@ -11376,10 +11604,14 @@
         </is>
       </c>
       <c r="BB49" s="36" t="n"/>
-      <c r="BC49" s="36" t="n"/>
+      <c r="BC49" s="36" t="inlineStr">
+        <is>
+          <t>RCT</t>
+        </is>
+      </c>
       <c r="BD49" s="40" t="inlineStr">
         <is>
-          <t>未填入</t>
+          <t>已填入</t>
         </is>
       </c>
       <c r="BE49" s="40" t="inlineStr">
@@ -11494,7 +11726,11 @@
           <t>自制</t>
         </is>
       </c>
-      <c r="AD50" s="38" t="n"/>
+      <c r="AD50" s="38" t="inlineStr">
+        <is>
+          <t>实验室</t>
+        </is>
+      </c>
       <c r="AE50" t="n">
         <v>5</v>
       </c>
@@ -11585,10 +11821,14 @@
         </is>
       </c>
       <c r="BB50" s="38" t="n"/>
-      <c r="BC50" s="38" t="n"/>
+      <c r="BC50" s="38" t="inlineStr">
+        <is>
+          <t>RCT</t>
+        </is>
+      </c>
       <c r="BD50" s="40" t="inlineStr">
         <is>
-          <t>未填入</t>
+          <t>已填入</t>
         </is>
       </c>
       <c r="BE50" s="40" t="inlineStr">
@@ -11696,7 +11936,11 @@
           <t>自制</t>
         </is>
       </c>
-      <c r="AD51" s="36" t="n"/>
+      <c r="AD51" s="36" t="inlineStr">
+        <is>
+          <t>实验室</t>
+        </is>
+      </c>
       <c r="AE51" t="n">
         <v>3</v>
       </c>
@@ -11787,10 +12031,14 @@
         </is>
       </c>
       <c r="BB51" s="36" t="n"/>
-      <c r="BC51" s="36" t="n"/>
+      <c r="BC51" s="36" t="inlineStr">
+        <is>
+          <t>RCT</t>
+        </is>
+      </c>
       <c r="BD51" s="40" t="inlineStr">
         <is>
-          <t>未填入</t>
+          <t>已填入</t>
         </is>
       </c>
       <c r="BE51" s="40" t="inlineStr">
@@ -11903,7 +12151,11 @@
           <t>Posit Science (IMPACT)</t>
         </is>
       </c>
-      <c r="AD52" s="38" t="n"/>
+      <c r="AD52" s="38" t="inlineStr">
+        <is>
+          <t>实验室</t>
+        </is>
+      </c>
       <c r="AF52" s="38" t="inlineStr">
         <is>
           <t>是</t>
@@ -11991,10 +12243,14 @@
         </is>
       </c>
       <c r="BB52" s="38" t="n"/>
-      <c r="BC52" s="38" t="n"/>
+      <c r="BC52" s="38" t="inlineStr">
+        <is>
+          <t>准RCT</t>
+        </is>
+      </c>
       <c r="BD52" s="40" t="inlineStr">
         <is>
-          <t>未填入</t>
+          <t>已填入</t>
         </is>
       </c>
       <c r="BE52" s="40" t="inlineStr">
@@ -12107,7 +12363,11 @@
           <t>自制</t>
         </is>
       </c>
-      <c r="AD53" s="36" t="n"/>
+      <c r="AD53" s="36" t="inlineStr">
+        <is>
+          <t>实验室</t>
+        </is>
+      </c>
       <c r="AE53" t="n">
         <v>2</v>
       </c>
@@ -12206,10 +12466,14 @@
         </is>
       </c>
       <c r="BB53" s="36" t="n"/>
-      <c r="BC53" s="36" t="n"/>
+      <c r="BC53" s="36" t="inlineStr">
+        <is>
+          <t>RCT</t>
+        </is>
+      </c>
       <c r="BD53" s="40" t="inlineStr">
         <is>
-          <t>未填入</t>
+          <t>已填入</t>
         </is>
       </c>
       <c r="BE53" s="40" t="inlineStr">
@@ -12324,7 +12588,11 @@
           <t>自制</t>
         </is>
       </c>
-      <c r="AD54" s="38" t="n"/>
+      <c r="AD54" s="38" t="inlineStr">
+        <is>
+          <t>实验室</t>
+        </is>
+      </c>
       <c r="AE54" t="n">
         <v>3</v>
       </c>
@@ -12413,10 +12681,14 @@
         </is>
       </c>
       <c r="BB54" s="38" t="n"/>
-      <c r="BC54" s="38" t="n"/>
+      <c r="BC54" s="38" t="inlineStr">
+        <is>
+          <t>RCT</t>
+        </is>
+      </c>
       <c r="BD54" s="40" t="inlineStr">
         <is>
-          <t>未填入</t>
+          <t>已填入</t>
         </is>
       </c>
       <c r="BE54" s="40" t="inlineStr">
@@ -12531,7 +12803,11 @@
           <t>自制</t>
         </is>
       </c>
-      <c r="AD55" s="36" t="n"/>
+      <c r="AD55" s="36" t="inlineStr">
+        <is>
+          <t>实验室</t>
+        </is>
+      </c>
       <c r="AE55" t="n">
         <v>2</v>
       </c>
@@ -12622,10 +12898,14 @@
         </is>
       </c>
       <c r="BB55" s="36" t="n"/>
-      <c r="BC55" s="36" t="n"/>
+      <c r="BC55" s="36" t="inlineStr">
+        <is>
+          <t>RCT</t>
+        </is>
+      </c>
       <c r="BD55" s="40" t="inlineStr">
         <is>
-          <t>未填入</t>
+          <t>已填入</t>
         </is>
       </c>
       <c r="BE55" s="40" t="inlineStr">
@@ -12740,7 +13020,11 @@
           <t>自制</t>
         </is>
       </c>
-      <c r="AD56" s="38" t="n"/>
+      <c r="AD56" s="38" t="inlineStr">
+        <is>
+          <t>实验室</t>
+        </is>
+      </c>
       <c r="AE56" t="n">
         <v>2.5</v>
       </c>
@@ -12839,10 +13123,14 @@
         </is>
       </c>
       <c r="BB56" s="38" t="n"/>
-      <c r="BC56" s="38" t="n"/>
+      <c r="BC56" s="38" t="inlineStr">
+        <is>
+          <t>RCT</t>
+        </is>
+      </c>
       <c r="BD56" s="40" t="inlineStr">
         <is>
-          <t>未填入</t>
+          <t>已填入</t>
         </is>
       </c>
       <c r="BE56" s="40" t="inlineStr">
@@ -12957,7 +13245,11 @@
           <t>自制</t>
         </is>
       </c>
-      <c r="AD57" s="36" t="n"/>
+      <c r="AD57" s="36" t="inlineStr">
+        <is>
+          <t>实验室</t>
+        </is>
+      </c>
       <c r="AE57" t="n">
         <v>2</v>
       </c>
@@ -13048,10 +13340,14 @@
         </is>
       </c>
       <c r="BB57" s="36" t="n"/>
-      <c r="BC57" s="36" t="n"/>
+      <c r="BC57" s="36" t="inlineStr">
+        <is>
+          <t>RCT</t>
+        </is>
+      </c>
       <c r="BD57" s="40" t="inlineStr">
         <is>
-          <t>未填入</t>
+          <t>已填入</t>
         </is>
       </c>
       <c r="BE57" s="40" t="inlineStr">
@@ -13166,7 +13462,11 @@
           <t>自制</t>
         </is>
       </c>
-      <c r="AD58" s="38" t="n"/>
+      <c r="AD58" s="38" t="inlineStr">
+        <is>
+          <t>实验室</t>
+        </is>
+      </c>
       <c r="AE58" t="n">
         <v>5</v>
       </c>
@@ -13257,10 +13557,14 @@
         </is>
       </c>
       <c r="BB58" s="38" t="n"/>
-      <c r="BC58" s="38" t="n"/>
+      <c r="BC58" s="38" t="inlineStr">
+        <is>
+          <t>RCT</t>
+        </is>
+      </c>
       <c r="BD58" s="40" t="inlineStr">
         <is>
-          <t>未填入</t>
+          <t>已填入</t>
         </is>
       </c>
       <c r="BE58" s="40" t="inlineStr">

--- a/projects/paper-01/04-extract/数据_6_数据提取表_v3_xhs.xlsx
+++ b/projects/paper-01/04-extract/数据_6_数据提取表_v3_xhs.xlsx
@@ -1412,28 +1412,44 @@
           <t>社区</t>
         </is>
       </c>
-      <c r="H3" s="36" t="n">
-        <v>42</v>
-      </c>
-      <c r="I3" s="36" t="n"/>
-      <c r="J3" s="36" t="n"/>
-      <c r="K3" s="36" t="n">
-        <v>67.93000000000001</v>
+      <c r="H3" s="36" t="inlineStr">
+        <is>
+          <t>42</t>
+        </is>
+      </c>
+      <c r="I3" s="36" t="inlineStr">
+        <is>
+          <t>42 (单组)</t>
+        </is>
+      </c>
+      <c r="J3" s="36" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="K3" s="36" t="inlineStr">
+        <is>
+          <t>67.93</t>
+        </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
           <t>young-old</t>
         </is>
       </c>
-      <c r="M3" s="36" t="n">
-        <v>5.57</v>
-      </c>
-      <c r="N3" s="36" t="n">
-        <v>50</v>
+      <c r="M3" s="36" t="inlineStr">
+        <is>
+          <t>5.57</t>
+        </is>
+      </c>
+      <c r="N3" s="36" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
       </c>
       <c r="O3" s="36" t="inlineStr">
         <is>
-          <t>未报告(7级量表)</t>
+          <t>7级量表(未转换)</t>
         </is>
       </c>
       <c r="P3" s="36" t="inlineStr">
@@ -1441,8 +1457,10 @@
           <t>MMSE</t>
         </is>
       </c>
-      <c r="Q3" s="36" t="n">
-        <v>29.58</v>
+      <c r="Q3" s="36" t="inlineStr">
+        <is>
+          <t>29.58</t>
+        </is>
       </c>
       <c r="R3" s="36" t="inlineStr">
         <is>
@@ -1470,7 +1488,7 @@
       <c r="W3" s="35" t="n"/>
       <c r="X3" s="36" t="inlineStr">
         <is>
-          <t>≤30天</t>
+          <t>30天内(约4周)</t>
         </is>
       </c>
       <c r="Y3" s="36" t="inlineStr">
@@ -1478,7 +1496,11 @@
           <t>否</t>
         </is>
       </c>
-      <c r="Z3" s="36" t="n"/>
+      <c r="Z3" s="36" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
       <c r="AA3" s="36" t="inlineStr">
         <is>
           <t>无</t>
@@ -1487,7 +1509,7 @@
       <c r="AB3" s="35" t="n"/>
       <c r="AC3" s="36" t="inlineStr">
         <is>
-          <t>自制</t>
+          <t>未明确</t>
         </is>
       </c>
       <c r="AD3" s="36" t="inlineStr">
@@ -1502,7 +1524,7 @@
       </c>
       <c r="AG3" s="36" t="inlineStr">
         <is>
-          <t>Backward Digit Span</t>
+          <t>训练任务本身</t>
         </is>
       </c>
       <c r="AH3" s="36" t="inlineStr">
@@ -1512,7 +1534,7 @@
       </c>
       <c r="AI3" s="36" t="inlineStr">
         <is>
-          <t>Faces &amp; Names; Shopping List</t>
+          <t>Faces and names task; Shopping list task</t>
         </is>
       </c>
       <c r="AJ3" s="36" t="n"/>
@@ -1521,11 +1543,7 @@
           <t>否</t>
         </is>
       </c>
-      <c r="AL3" s="36" t="inlineStr">
-        <is>
-          <t>未报告</t>
-        </is>
-      </c>
+      <c r="AL3" s="36" t="inlineStr"/>
       <c r="AM3" s="35" t="inlineStr">
         <is>
           <t>否</t>
@@ -1543,7 +1561,7 @@
         </is>
       </c>
       <c r="AQ3" s="36" t="n"/>
-      <c r="AR3" s="36" t="n"/>
+      <c r="AR3" s="36" t="inlineStr"/>
       <c r="AS3" s="36" t="inlineStr">
         <is>
           <t>高/低</t>
@@ -1630,11 +1648,21 @@
           <t>社区</t>
         </is>
       </c>
-      <c r="H4" s="38" t="n">
-        <v>72</v>
-      </c>
-      <c r="I4" s="38" t="n"/>
-      <c r="J4" s="38" t="n"/>
+      <c r="H4" s="38" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="I4" s="38" t="inlineStr">
+        <is>
+          <t>54 (3组: 19+19+16)</t>
+        </is>
+      </c>
+      <c r="J4" s="38" t="inlineStr">
+        <is>
+          <t>18 (Active control)</t>
+        </is>
+      </c>
       <c r="K4" s="38" t="n">
         <v>69.23999999999999</v>
       </c>
@@ -1669,7 +1697,7 @@
       </c>
       <c r="S4" s="38" t="inlineStr">
         <is>
-          <t>Categorization WM Span (verbal)</t>
+          <t>Categorization WM Span</t>
         </is>
       </c>
       <c r="T4" s="38" t="inlineStr">
@@ -1692,7 +1720,11 @@
           <t>是</t>
         </is>
       </c>
-      <c r="Z4" s="38" t="n"/>
+      <c r="Z4" s="38" t="inlineStr">
+        <is>
+          <t>Active control (其他活动)</t>
+        </is>
+      </c>
       <c r="AA4" s="38" t="inlineStr">
         <is>
           <t>无</t>
@@ -1845,8 +1877,10 @@
           <t>社区/大学</t>
         </is>
       </c>
-      <c r="H5" s="36" t="n">
-        <v>46</v>
+      <c r="H5" s="36" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
       </c>
       <c r="I5" s="36" t="n"/>
       <c r="J5" s="36" t="n"/>
@@ -1903,7 +1937,7 @@
       <c r="W5" s="35" t="n"/>
       <c r="X5" s="36" t="inlineStr">
         <is>
-          <t>3-6</t>
+          <t>6</t>
         </is>
       </c>
       <c r="Y5" s="36" t="inlineStr">
@@ -2063,8 +2097,10 @@
           <t>社区</t>
         </is>
       </c>
-      <c r="H6" s="38" t="n">
-        <v>72</v>
+      <c r="H6" s="38" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
       </c>
       <c r="I6" s="38" t="n"/>
       <c r="J6" s="38" t="n"/>
@@ -2115,8 +2151,10 @@
         <v>60</v>
       </c>
       <c r="W6" s="37" t="n"/>
-      <c r="X6" s="38" t="n">
-        <v>2</v>
+      <c r="X6" s="38" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
       </c>
       <c r="Y6" s="38" t="inlineStr">
         <is>
@@ -2276,13 +2314,17 @@
           <t>社区</t>
         </is>
       </c>
-      <c r="H7" s="36" t="n">
-        <v>28</v>
+      <c r="H7" s="36" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
       </c>
       <c r="I7" s="36" t="n"/>
       <c r="J7" s="36" t="n"/>
-      <c r="K7" s="36" t="n">
-        <v>63.11</v>
+      <c r="K7" s="36" t="inlineStr">
+        <is>
+          <t>25.44</t>
+        </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
@@ -2291,7 +2333,7 @@
       </c>
       <c r="M7" s="36" t="inlineStr">
         <is>
-          <t>未报告</t>
+          <t>3.32</t>
         </is>
       </c>
       <c r="N7" s="36" t="n">
@@ -2334,8 +2376,10 @@
         <v>30</v>
       </c>
       <c r="W7" s="35" t="n"/>
-      <c r="X7" s="36" t="n">
-        <v>3</v>
+      <c r="X7" s="36" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
       </c>
       <c r="Y7" s="36" t="inlineStr">
         <is>
@@ -2565,7 +2609,11 @@
           <t>是</t>
         </is>
       </c>
-      <c r="Z8" s="38" t="n"/>
+      <c r="Z8" s="38" t="inlineStr">
+        <is>
+          <t>Active control</t>
+        </is>
+      </c>
       <c r="AA8" s="38" t="inlineStr">
         <is>
           <t>无</t>
@@ -2718,8 +2766,10 @@
           <t>社区</t>
         </is>
       </c>
-      <c r="H9" s="36" t="n">
-        <v>76</v>
+      <c r="H9" s="36" t="inlineStr">
+        <is>
+          <t>46</t>
+        </is>
       </c>
       <c r="I9" s="36" t="n"/>
       <c r="J9" s="36" t="n"/>
@@ -2740,7 +2790,7 @@
       </c>
       <c r="O9" s="36" t="inlineStr">
         <is>
-          <t>≥6年</t>
+          <t>6</t>
         </is>
       </c>
       <c r="P9" s="36" t="inlineStr">
@@ -2775,15 +2825,21 @@
         <v>60</v>
       </c>
       <c r="W9" s="35" t="n"/>
-      <c r="X9" s="36" t="n">
-        <v>6</v>
+      <c r="X9" s="36" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
       </c>
       <c r="Y9" s="36" t="inlineStr">
         <is>
           <t>是</t>
         </is>
       </c>
-      <c r="Z9" s="36" t="n"/>
+      <c r="Z9" s="36" t="inlineStr">
+        <is>
+          <t>Active control</t>
+        </is>
+      </c>
       <c r="AA9" s="36" t="inlineStr">
         <is>
           <t>无</t>
@@ -2944,21 +3000,27 @@
           <t>社区</t>
         </is>
       </c>
-      <c r="H10" s="38" t="n">
-        <v>142</v>
+      <c r="H10" s="38" t="inlineStr">
+        <is>
+          <t>191</t>
+        </is>
       </c>
       <c r="I10" s="38" t="n"/>
       <c r="J10" s="38" t="n"/>
-      <c r="K10" s="38" t="n">
-        <v>70.34999999999999</v>
+      <c r="K10" s="38" t="inlineStr">
+        <is>
+          <t>74</t>
+        </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
           <t>young-old</t>
         </is>
       </c>
-      <c r="M10" s="38" t="n">
-        <v>3.66</v>
+      <c r="M10" s="38" t="inlineStr">
+        <is>
+          <t>48</t>
+        </is>
       </c>
       <c r="N10" s="38" t="n">
         <v>48</v>
@@ -3010,7 +3072,11 @@
           <t>是</t>
         </is>
       </c>
-      <c r="Z10" s="38" t="n"/>
+      <c r="Z10" s="38" t="inlineStr">
+        <is>
+          <t>Active control</t>
+        </is>
+      </c>
       <c r="AA10" s="38" t="inlineStr">
         <is>
           <t>无</t>
@@ -3165,21 +3231,27 @@
           <t>社区</t>
         </is>
       </c>
-      <c r="H11" s="36" t="n">
-        <v>54</v>
+      <c r="H11" s="36" t="inlineStr">
+        <is>
+          <t>108</t>
+        </is>
       </c>
       <c r="I11" s="36" t="n"/>
       <c r="J11" s="36" t="n"/>
-      <c r="K11" s="36" t="n">
-        <v>68.2</v>
+      <c r="K11" s="36" t="inlineStr">
+        <is>
+          <t>5.92</t>
+        </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
           <t>young-old</t>
         </is>
       </c>
-      <c r="M11" s="36" t="n">
-        <v>5.92</v>
+      <c r="M11" s="36" t="inlineStr">
+        <is>
+          <t>41</t>
+        </is>
       </c>
       <c r="N11" s="36" t="n">
         <v>76</v>
@@ -3225,7 +3297,7 @@
       <c r="W11" s="35" t="n"/>
       <c r="X11" s="36" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="Y11" s="36" t="inlineStr">
@@ -3386,8 +3458,10 @@
           <t>社区</t>
         </is>
       </c>
-      <c r="H12" s="38" t="n">
-        <v>26</v>
+      <c r="H12" s="38" t="inlineStr">
+        <is>
+          <t>45</t>
+        </is>
       </c>
       <c r="I12" s="38" t="n"/>
       <c r="J12" s="38" t="n"/>
@@ -3607,8 +3681,10 @@
           <t>社区</t>
         </is>
       </c>
-      <c r="H13" s="36" t="n">
-        <v>90</v>
+      <c r="H13" s="36" t="inlineStr">
+        <is>
+          <t>89</t>
+        </is>
       </c>
       <c r="I13" s="36" t="n"/>
       <c r="J13" s="36" t="n"/>
@@ -3836,8 +3912,10 @@
           <t>社区</t>
         </is>
       </c>
-      <c r="H14" s="38" t="n">
-        <v>83</v>
+      <c r="H14" s="38" t="inlineStr">
+        <is>
+          <t>83</t>
+        </is>
       </c>
       <c r="I14" s="38" t="n"/>
       <c r="J14" s="38" t="n"/>
@@ -3893,8 +3971,10 @@
         </is>
       </c>
       <c r="W14" s="37" t="n"/>
-      <c r="X14" s="38" t="n">
-        <v>5</v>
+      <c r="X14" s="38" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
       </c>
       <c r="Y14" s="38" t="inlineStr">
         <is>
@@ -4056,8 +4136,10 @@
           <t>社区</t>
         </is>
       </c>
-      <c r="H15" s="36" t="n">
-        <v>25</v>
+      <c r="H15" s="36" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
       </c>
       <c r="I15" s="36" t="n"/>
       <c r="J15" s="36" t="n"/>
@@ -4277,8 +4359,10 @@
           <t>社区</t>
         </is>
       </c>
-      <c r="H16" s="38" t="n">
-        <v>32</v>
+      <c r="H16" s="38" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
       </c>
       <c r="I16" s="38" t="n"/>
       <c r="J16" s="38" t="n"/>
@@ -4493,8 +4577,10 @@
           <t>社区</t>
         </is>
       </c>
-      <c r="H17" s="36" t="n">
-        <v>85</v>
+      <c r="H17" s="36" t="inlineStr">
+        <is>
+          <t>43</t>
+        </is>
       </c>
       <c r="I17" s="36" t="n"/>
       <c r="J17" s="36" t="n"/>
@@ -4716,8 +4802,10 @@
           <t>社区</t>
         </is>
       </c>
-      <c r="H18" s="38" t="n">
-        <v>30</v>
+      <c r="H18" s="38" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
       </c>
       <c r="I18" s="38" t="n"/>
       <c r="J18" s="38" t="n"/>
@@ -4937,8 +5025,10 @@
           <t>社区</t>
         </is>
       </c>
-      <c r="H19" s="36" t="n">
-        <v>36</v>
+      <c r="H19" s="36" t="inlineStr">
+        <is>
+          <t>36</t>
+        </is>
       </c>
       <c r="I19" s="36" t="n"/>
       <c r="J19" s="36" t="n"/>
@@ -5155,8 +5245,10 @@
           <t>医院/社区</t>
         </is>
       </c>
-      <c r="H20" s="38" t="n">
-        <v>20</v>
+      <c r="H20" s="38" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
       </c>
       <c r="I20" s="38" t="n"/>
       <c r="J20" s="38" t="n"/>
@@ -5430,8 +5522,10 @@
         <v>60</v>
       </c>
       <c r="W21" s="35" t="n"/>
-      <c r="X21" s="36" t="n">
-        <v>10</v>
+      <c r="X21" s="36" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
       </c>
       <c r="Y21" s="36" t="inlineStr">
         <is>
@@ -5593,8 +5687,10 @@
           <t>社区</t>
         </is>
       </c>
-      <c r="H22" s="38" t="n">
-        <v>62</v>
+      <c r="H22" s="38" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
       </c>
       <c r="I22" s="38" t="n"/>
       <c r="J22" s="38" t="n"/>
@@ -5814,8 +5910,10 @@
           <t>社区</t>
         </is>
       </c>
-      <c r="H23" s="36" t="n">
-        <v>30</v>
+      <c r="H23" s="36" t="inlineStr">
+        <is>
+          <t>51</t>
+        </is>
       </c>
       <c r="I23" s="36" t="n"/>
       <c r="J23" s="36" t="n"/>
@@ -6038,21 +6136,27 @@
           <t>社区(在线)</t>
         </is>
       </c>
-      <c r="H24" s="38" t="n">
-        <v>104</v>
+      <c r="H24" s="38" t="inlineStr">
+        <is>
+          <t>36</t>
+        </is>
       </c>
       <c r="I24" s="38" t="n"/>
       <c r="J24" s="38" t="n"/>
-      <c r="K24" s="38" t="n">
-        <v>68.2</v>
+      <c r="K24" s="38" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
       </c>
       <c r="L24" t="inlineStr">
         <is>
           <t>young-old</t>
         </is>
       </c>
-      <c r="M24" s="38" t="n">
-        <v>3</v>
+      <c r="M24" s="38" t="inlineStr">
+        <is>
+          <t>2.73</t>
+        </is>
       </c>
       <c r="N24" s="38" t="n">
         <v>48</v>
@@ -6251,8 +6355,10 @@
           <t>社区</t>
         </is>
       </c>
-      <c r="H25" s="36" t="n">
-        <v>80</v>
+      <c r="H25" s="36" t="inlineStr">
+        <is>
+          <t>80</t>
+        </is>
       </c>
       <c r="I25" s="36" t="n"/>
       <c r="J25" s="36" t="n"/>
@@ -6307,8 +6413,10 @@
         <v>30</v>
       </c>
       <c r="W25" s="35" t="n"/>
-      <c r="X25" s="36" t="n">
-        <v>3</v>
+      <c r="X25" s="36" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
       </c>
       <c r="Y25" s="36" t="inlineStr">
         <is>
@@ -6468,8 +6576,10 @@
           <t>社区</t>
         </is>
       </c>
-      <c r="H26" s="38" t="n">
-        <v>21</v>
+      <c r="H26" s="38" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
       </c>
       <c r="I26" s="38" t="n"/>
       <c r="J26" s="38" t="n"/>
@@ -6685,8 +6795,10 @@
           <t>社区</t>
         </is>
       </c>
-      <c r="H27" s="36" t="n">
-        <v>54</v>
+      <c r="H27" s="36" t="inlineStr">
+        <is>
+          <t>116</t>
+        </is>
       </c>
       <c r="I27" s="36" t="n"/>
       <c r="J27" s="36" t="n"/>
@@ -6908,8 +7020,10 @@
           <t>社区</t>
         </is>
       </c>
-      <c r="H28" s="38" t="n">
-        <v>183</v>
+      <c r="H28" s="38" t="inlineStr">
+        <is>
+          <t>183</t>
+        </is>
       </c>
       <c r="I28" s="38" t="n"/>
       <c r="J28" s="38" t="n"/>
@@ -7127,8 +7241,10 @@
           <t>大学</t>
         </is>
       </c>
-      <c r="H29" s="36" t="n">
-        <v>65</v>
+      <c r="H29" s="36" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
       </c>
       <c r="I29" s="36" t="n"/>
       <c r="J29" s="36" t="n"/>
@@ -7341,8 +7457,10 @@
           <t>社区</t>
         </is>
       </c>
-      <c r="H30" s="38" t="n">
-        <v>36</v>
+      <c r="H30" s="38" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
       </c>
       <c r="I30" s="38" t="n"/>
       <c r="J30" s="38" t="n"/>
@@ -7560,8 +7678,10 @@
           <t>社区</t>
         </is>
       </c>
-      <c r="H31" s="36" t="n">
-        <v>37</v>
+      <c r="H31" s="36" t="inlineStr">
+        <is>
+          <t>012</t>
+        </is>
       </c>
       <c r="I31" s="36" t="n"/>
       <c r="J31" s="36" t="n"/>
@@ -7781,8 +7901,10 @@
           <t>医院</t>
         </is>
       </c>
-      <c r="H32" s="38" t="n">
-        <v>40</v>
+      <c r="H32" s="38" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
       </c>
       <c r="I32" s="38" t="n"/>
       <c r="J32" s="38" t="n"/>
@@ -7831,8 +7953,10 @@
       </c>
       <c r="V32" s="38" t="n"/>
       <c r="W32" s="37" t="n"/>
-      <c r="X32" s="38" t="n">
-        <v>2</v>
+      <c r="X32" s="38" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
       </c>
       <c r="Y32" s="38" t="inlineStr">
         <is>
@@ -7990,8 +8114,10 @@
           <t>社区</t>
         </is>
       </c>
-      <c r="H33" s="36" t="n">
-        <v>28</v>
+      <c r="H33" s="36" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
       </c>
       <c r="I33" s="36" t="n"/>
       <c r="J33" s="36" t="n"/>
@@ -8201,8 +8327,10 @@
           <t>养老院</t>
         </is>
       </c>
-      <c r="H34" s="38" t="n">
-        <v>19</v>
+      <c r="H34" s="38" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
       </c>
       <c r="I34" s="38" t="n"/>
       <c r="J34" s="38" t="n"/>
@@ -8418,8 +8546,10 @@
           <t>社区</t>
         </is>
       </c>
-      <c r="H35" s="36" t="n">
-        <v>119</v>
+      <c r="H35" s="36" t="inlineStr">
+        <is>
+          <t>140</t>
+        </is>
       </c>
       <c r="I35" s="36" t="n"/>
       <c r="J35" s="36" t="n"/>
@@ -8635,8 +8765,10 @@
           <t>社区</t>
         </is>
       </c>
-      <c r="H36" s="38" t="n">
-        <v>39</v>
+      <c r="H36" s="38" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
       </c>
       <c r="I36" s="38" t="n"/>
       <c r="J36" s="38" t="n"/>
@@ -8854,8 +8986,10 @@
           <t>社区</t>
         </is>
       </c>
-      <c r="H37" s="36" t="n">
-        <v>71</v>
+      <c r="H37" s="36" t="inlineStr">
+        <is>
+          <t>34</t>
+        </is>
       </c>
       <c r="I37" s="36" t="n"/>
       <c r="J37" s="36" t="n"/>
@@ -9065,21 +9199,27 @@
           <t>社区</t>
         </is>
       </c>
-      <c r="H38" s="38" t="n">
-        <v>34</v>
+      <c r="H38" s="38" t="inlineStr">
+        <is>
+          <t>34</t>
+        </is>
       </c>
       <c r="I38" s="38" t="n"/>
       <c r="J38" s="38" t="n"/>
-      <c r="K38" s="38" t="n">
-        <v>65.78</v>
+      <c r="K38" s="38" t="inlineStr">
+        <is>
+          <t>78</t>
+        </is>
       </c>
       <c r="L38" t="inlineStr">
         <is>
           <t>young-old</t>
         </is>
       </c>
-      <c r="M38" s="38" t="n">
-        <v>3.04</v>
+      <c r="M38" s="38" t="inlineStr">
+        <is>
+          <t>3.04</t>
+        </is>
       </c>
       <c r="N38" s="38" t="n">
         <v>61</v>
@@ -9117,8 +9257,10 @@
       </c>
       <c r="V38" s="38" t="n"/>
       <c r="W38" s="37" t="n"/>
-      <c r="X38" s="38" t="n">
-        <v>4</v>
+      <c r="X38" s="38" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
       </c>
       <c r="Y38" s="38" t="inlineStr">
         <is>
@@ -9288,8 +9430,10 @@
           <t>社区</t>
         </is>
       </c>
-      <c r="H39" s="36" t="n">
-        <v>137</v>
+      <c r="H39" s="36" t="inlineStr">
+        <is>
+          <t>146</t>
+        </is>
       </c>
       <c r="I39" s="36" t="n"/>
       <c r="J39" s="36" t="n"/>
@@ -9500,8 +9644,10 @@
           <t>社区</t>
         </is>
       </c>
-      <c r="H40" s="38" t="n">
-        <v>103</v>
+      <c r="H40" s="38" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
       </c>
       <c r="I40" s="38" t="n"/>
       <c r="J40" s="38" t="n"/>
@@ -9710,8 +9856,10 @@
           <t>社区</t>
         </is>
       </c>
-      <c r="H41" s="36" t="n">
-        <v>35</v>
+      <c r="H41" s="36" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
       </c>
       <c r="I41" s="36" t="n"/>
       <c r="J41" s="36" t="n"/>
@@ -9933,8 +10081,10 @@
           <t>社区</t>
         </is>
       </c>
-      <c r="H42" s="38" t="n">
-        <v>36</v>
+      <c r="H42" s="38" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
       </c>
       <c r="I42" s="38" t="n"/>
       <c r="J42" s="38" t="n"/>
@@ -10148,8 +10298,10 @@
           <t>社区</t>
         </is>
       </c>
-      <c r="H43" s="36" t="n">
-        <v>97</v>
+      <c r="H43" s="36" t="inlineStr">
+        <is>
+          <t>125</t>
+        </is>
       </c>
       <c r="I43" s="36" t="n"/>
       <c r="J43" s="36" t="n"/>
@@ -10357,8 +10509,10 @@
           <t>社区</t>
         </is>
       </c>
-      <c r="H44" s="38" t="n">
-        <v>30</v>
+      <c r="H44" s="38" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
       </c>
       <c r="I44" s="38" t="n"/>
       <c r="J44" s="38" t="n"/>
@@ -10582,8 +10736,10 @@
           <t>社区</t>
         </is>
       </c>
-      <c r="H45" s="36" t="n">
-        <v>97</v>
+      <c r="H45" s="36" t="inlineStr">
+        <is>
+          <t>125</t>
+        </is>
       </c>
       <c r="I45" s="36" t="n"/>
       <c r="J45" s="36" t="n"/>
@@ -10795,8 +10951,10 @@
           <t>社区</t>
         </is>
       </c>
-      <c r="H46" s="38" t="n">
-        <v>36</v>
+      <c r="H46" s="38" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
       </c>
       <c r="I46" s="38" t="n"/>
       <c r="J46" s="38" t="n"/>
@@ -11014,8 +11172,10 @@
           <t>社区</t>
         </is>
       </c>
-      <c r="H47" s="36" t="n">
-        <v>43</v>
+      <c r="H47" s="36" t="inlineStr">
+        <is>
+          <t>46</t>
+        </is>
       </c>
       <c r="I47" s="36" t="n"/>
       <c r="J47" s="36" t="n"/>
@@ -11064,7 +11224,11 @@
       <c r="U47" s="36" t="n"/>
       <c r="V47" s="36" t="n"/>
       <c r="W47" s="35" t="n"/>
-      <c r="X47" s="36" t="n"/>
+      <c r="X47" s="36" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="Y47" s="36" t="inlineStr">
         <is>
           <t>是</t>
@@ -11222,8 +11386,10 @@
           <t>社区</t>
         </is>
       </c>
-      <c r="H48" s="38" t="n">
-        <v>119</v>
+      <c r="H48" s="38" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
       </c>
       <c r="I48" s="38" t="n"/>
       <c r="J48" s="38" t="n"/>
@@ -11439,8 +11605,10 @@
           <t>社区</t>
         </is>
       </c>
-      <c r="H49" s="36" t="n">
-        <v>148</v>
+      <c r="H49" s="36" t="inlineStr">
+        <is>
+          <t>148</t>
+        </is>
       </c>
       <c r="I49" s="36" t="n"/>
       <c r="J49" s="36" t="n"/>
@@ -11652,8 +11820,10 @@
           <t>社区</t>
         </is>
       </c>
-      <c r="H50" s="38" t="n">
-        <v>47</v>
+      <c r="H50" s="38" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
       </c>
       <c r="I50" s="38" t="n"/>
       <c r="J50" s="38" t="n"/>
@@ -11869,8 +12039,10 @@
           <t>社区</t>
         </is>
       </c>
-      <c r="H51" s="36" t="n">
-        <v>56</v>
+      <c r="H51" s="36" t="inlineStr">
+        <is>
+          <t>56</t>
+        </is>
       </c>
       <c r="I51" s="36" t="n"/>
       <c r="J51" s="36" t="n"/>
@@ -11916,8 +12088,10 @@
         <v>20</v>
       </c>
       <c r="W51" s="35" t="n"/>
-      <c r="X51" s="36" t="n">
-        <v>3</v>
+      <c r="X51" s="36" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
       </c>
       <c r="Y51" s="36" t="inlineStr">
         <is>
@@ -12079,8 +12253,10 @@
           <t>社区</t>
         </is>
       </c>
-      <c r="H52" s="38" t="n">
-        <v>487</v>
+      <c r="H52" s="38" t="inlineStr">
+        <is>
+          <t>242</t>
+        </is>
       </c>
       <c r="I52" s="38" t="n"/>
       <c r="J52" s="38" t="n"/>
@@ -12291,8 +12467,10 @@
           <t>社区</t>
         </is>
       </c>
-      <c r="H53" s="36" t="n">
-        <v>24</v>
+      <c r="H53" s="36" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
       </c>
       <c r="I53" s="36" t="n"/>
       <c r="J53" s="36" t="n"/>
@@ -12514,8 +12692,10 @@
           <t>社区</t>
         </is>
       </c>
-      <c r="H54" s="38" t="n">
-        <v>66</v>
+      <c r="H54" s="38" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
       </c>
       <c r="I54" s="38" t="n"/>
       <c r="J54" s="38" t="n"/>
@@ -12568,8 +12748,10 @@
         <v>45</v>
       </c>
       <c r="W54" s="37" t="n"/>
-      <c r="X54" s="38" t="n">
-        <v>4</v>
+      <c r="X54" s="38" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
       </c>
       <c r="Y54" s="38" t="inlineStr">
         <is>
@@ -12729,8 +12911,10 @@
           <t>社区</t>
         </is>
       </c>
-      <c r="H55" s="36" t="n">
-        <v>35</v>
+      <c r="H55" s="36" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
       </c>
       <c r="I55" s="36" t="n"/>
       <c r="J55" s="36" t="n"/>
@@ -12946,8 +13130,10 @@
           <t>社区</t>
         </is>
       </c>
-      <c r="H56" s="38" t="n">
-        <v>24</v>
+      <c r="H56" s="38" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
       </c>
       <c r="I56" s="38" t="n"/>
       <c r="J56" s="38" t="n"/>
@@ -13000,8 +13186,10 @@
         <v>30</v>
       </c>
       <c r="W56" s="37" t="n"/>
-      <c r="X56" s="38" t="n">
-        <v>4</v>
+      <c r="X56" s="38" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
       </c>
       <c r="Y56" s="38" t="inlineStr">
         <is>
@@ -13171,8 +13359,10 @@
           <t>社区</t>
         </is>
       </c>
-      <c r="H57" s="36" t="n">
-        <v>91</v>
+      <c r="H57" s="36" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
       </c>
       <c r="I57" s="36" t="n"/>
       <c r="J57" s="36" t="n"/>
@@ -13388,8 +13578,10 @@
           <t>社区</t>
         </is>
       </c>
-      <c r="H58" s="38" t="n">
-        <v>68</v>
+      <c r="H58" s="38" t="inlineStr">
+        <is>
+          <t>215</t>
+        </is>
       </c>
       <c r="I58" s="38" t="n"/>
       <c r="J58" s="38" t="n"/>

--- a/projects/paper-01/04-extract/数据_6_数据提取表_v3_xhs.xlsx
+++ b/projects/paper-01/04-extract/数据_6_数据提取表_v3_xhs.xlsx
@@ -1488,7 +1488,7 @@
       <c r="W3" s="35" t="n"/>
       <c r="X3" s="36" t="inlineStr">
         <is>
-          <t>30天内(约4周)</t>
+          <t>4</t>
         </is>
       </c>
       <c r="Y3" s="36" t="inlineStr">
@@ -1655,7 +1655,7 @@
       </c>
       <c r="I4" s="38" t="inlineStr">
         <is>
-          <t>54 (3组: 19+19+16)</t>
+          <t>54 (3组)</t>
         </is>
       </c>
       <c r="J4" s="38" t="inlineStr">
@@ -1663,19 +1663,25 @@
           <t>18 (Active control)</t>
         </is>
       </c>
-      <c r="K4" s="38" t="n">
-        <v>69.23999999999999</v>
+      <c r="K4" s="38" t="inlineStr">
+        <is>
+          <t>69.24</t>
+        </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
           <t>young-old</t>
         </is>
       </c>
-      <c r="M4" s="38" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="N4" s="38" t="n">
-        <v>58</v>
+      <c r="M4" s="38" t="inlineStr">
+        <is>
+          <t>3.1</t>
+        </is>
+      </c>
+      <c r="N4" s="38" t="inlineStr">
+        <is>
+          <t>58</t>
+        </is>
       </c>
       <c r="O4" s="38" t="n">
         <v>13.84</v>
@@ -1712,8 +1718,10 @@
         <v>60</v>
       </c>
       <c r="W4" s="37" t="n"/>
-      <c r="X4" s="38" t="n">
-        <v>2</v>
+      <c r="X4" s="38" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
       </c>
       <c r="Y4" s="38" t="inlineStr">
         <is>
@@ -1722,7 +1730,7 @@
       </c>
       <c r="Z4" s="38" t="inlineStr">
         <is>
-          <t>Active control (其他活动)</t>
+          <t>Active control</t>
         </is>
       </c>
       <c r="AA4" s="38" t="inlineStr">
@@ -1884,19 +1892,25 @@
       </c>
       <c r="I5" s="36" t="n"/>
       <c r="J5" s="36" t="n"/>
-      <c r="K5" s="36" t="n">
-        <v>64.8</v>
+      <c r="K5" s="36" t="inlineStr">
+        <is>
+          <t>27.5</t>
+        </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
           <t>young-old</t>
         </is>
       </c>
-      <c r="M5" s="36" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="N5" s="36" t="n">
-        <v>56</v>
+      <c r="M5" s="36" t="inlineStr">
+        <is>
+          <t>3.5</t>
+        </is>
+      </c>
+      <c r="N5" s="36" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
       </c>
       <c r="O5" s="36" t="inlineStr">
         <is>
@@ -1937,7 +1951,7 @@
       <c r="W5" s="35" t="n"/>
       <c r="X5" s="36" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>3</t>
         </is>
       </c>
       <c r="Y5" s="36" t="inlineStr">
@@ -3460,7 +3474,7 @@
       </c>
       <c r="H12" s="38" t="inlineStr">
         <is>
-          <t>45</t>
+          <t>64</t>
         </is>
       </c>
       <c r="I12" s="38" t="n"/>
@@ -3518,15 +3532,21 @@
         </is>
       </c>
       <c r="W12" s="37" t="n"/>
-      <c r="X12" s="38" t="n">
-        <v>5</v>
+      <c r="X12" s="38" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
       </c>
       <c r="Y12" s="38" t="inlineStr">
         <is>
           <t>是</t>
         </is>
       </c>
-      <c r="Z12" s="38" t="n"/>
+      <c r="Z12" s="38" t="inlineStr">
+        <is>
+          <t>Active control</t>
+        </is>
+      </c>
       <c r="AA12" s="38" t="inlineStr">
         <is>
           <t>无</t>
@@ -3981,7 +4001,11 @@
           <t>是</t>
         </is>
       </c>
-      <c r="Z14" s="38" t="n"/>
+      <c r="Z14" s="38" t="inlineStr">
+        <is>
+          <t>Active control</t>
+        </is>
+      </c>
       <c r="AA14" s="38" t="inlineStr">
         <is>
           <t>无</t>
@@ -4424,7 +4448,11 @@
           <t>是</t>
         </is>
       </c>
-      <c r="Z16" s="38" t="n"/>
+      <c r="Z16" s="38" t="inlineStr">
+        <is>
+          <t>Active control</t>
+        </is>
+      </c>
       <c r="AA16" s="38" t="inlineStr">
         <is>
           <t>无</t>
@@ -4639,15 +4667,21 @@
         <v>45</v>
       </c>
       <c r="W17" s="35" t="n"/>
-      <c r="X17" s="36" t="n">
-        <v>5</v>
+      <c r="X17" s="36" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
       </c>
       <c r="Y17" s="36" t="inlineStr">
         <is>
           <t>是</t>
         </is>
       </c>
-      <c r="Z17" s="36" t="n"/>
+      <c r="Z17" s="36" t="inlineStr">
+        <is>
+          <t>Active control</t>
+        </is>
+      </c>
       <c r="AA17" s="36" t="inlineStr">
         <is>
           <t>无</t>
@@ -4866,7 +4900,11 @@
           <t>是</t>
         </is>
       </c>
-      <c r="Z18" s="38" t="n"/>
+      <c r="Z18" s="38" t="inlineStr">
+        <is>
+          <t>Active control</t>
+        </is>
+      </c>
       <c r="AA18" s="38" t="inlineStr">
         <is>
           <t>无</t>
@@ -5092,7 +5130,11 @@
           <t>是</t>
         </is>
       </c>
-      <c r="Z19" s="36" t="n"/>
+      <c r="Z19" s="36" t="inlineStr">
+        <is>
+          <t>Active control</t>
+        </is>
+      </c>
       <c r="AA19" s="36" t="inlineStr">
         <is>
           <t>无</t>
@@ -5311,7 +5353,11 @@
           <t>是</t>
         </is>
       </c>
-      <c r="Z20" s="38" t="n"/>
+      <c r="Z20" s="38" t="inlineStr">
+        <is>
+          <t>Active control</t>
+        </is>
+      </c>
       <c r="AA20" s="38" t="inlineStr">
         <is>
           <t>无</t>
@@ -5977,7 +6023,11 @@
           <t>否</t>
         </is>
       </c>
-      <c r="Z23" s="36" t="n"/>
+      <c r="Z23" s="36" t="inlineStr">
+        <is>
+          <t>Active control</t>
+        </is>
+      </c>
       <c r="AA23" s="36" t="inlineStr">
         <is>
           <t>无</t>
@@ -6423,7 +6473,11 @@
           <t>是</t>
         </is>
       </c>
-      <c r="Z25" s="36" t="n"/>
+      <c r="Z25" s="36" t="inlineStr">
+        <is>
+          <t>Active control</t>
+        </is>
+      </c>
       <c r="AA25" s="36" t="inlineStr">
         <is>
           <t>无</t>
@@ -6644,7 +6698,11 @@
           <t>是</t>
         </is>
       </c>
-      <c r="Z26" s="38" t="n"/>
+      <c r="Z26" s="38" t="inlineStr">
+        <is>
+          <t>Active control</t>
+        </is>
+      </c>
       <c r="AA26" s="38" t="inlineStr">
         <is>
           <t>无</t>
@@ -6861,7 +6919,11 @@
           <t>是</t>
         </is>
       </c>
-      <c r="Z27" s="36" t="n"/>
+      <c r="Z27" s="36" t="inlineStr">
+        <is>
+          <t>Active control</t>
+        </is>
+      </c>
       <c r="AA27" s="36" t="inlineStr">
         <is>
           <t>无</t>
@@ -7305,7 +7367,11 @@
           <t>是</t>
         </is>
       </c>
-      <c r="Z29" s="36" t="n"/>
+      <c r="Z29" s="36" t="inlineStr">
+        <is>
+          <t>Active control</t>
+        </is>
+      </c>
       <c r="AA29" s="36" t="inlineStr">
         <is>
           <t>无</t>
@@ -7519,7 +7585,11 @@
           <t>是</t>
         </is>
       </c>
-      <c r="Z30" s="38" t="n"/>
+      <c r="Z30" s="38" t="inlineStr">
+        <is>
+          <t>Active control</t>
+        </is>
+      </c>
       <c r="AA30" s="38" t="inlineStr">
         <is>
           <t>无</t>
@@ -7955,7 +8025,7 @@
       <c r="W32" s="37" t="n"/>
       <c r="X32" s="38" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
         </is>
       </c>
       <c r="Y32" s="38" t="inlineStr">
@@ -8610,7 +8680,11 @@
           <t>是</t>
         </is>
       </c>
-      <c r="Z35" s="36" t="n"/>
+      <c r="Z35" s="36" t="inlineStr">
+        <is>
+          <t>Active control</t>
+        </is>
+      </c>
       <c r="AA35" s="36" t="inlineStr">
         <is>
           <t>无</t>
@@ -8827,7 +8901,11 @@
           <t>是</t>
         </is>
       </c>
-      <c r="Z36" s="38" t="n"/>
+      <c r="Z36" s="38" t="inlineStr">
+        <is>
+          <t>Active control</t>
+        </is>
+      </c>
       <c r="AA36" s="38" t="inlineStr">
         <is>
           <t>无</t>
@@ -9267,7 +9345,11 @@
           <t>是</t>
         </is>
       </c>
-      <c r="Z38" s="38" t="n"/>
+      <c r="Z38" s="38" t="inlineStr">
+        <is>
+          <t>Active control</t>
+        </is>
+      </c>
       <c r="AA38" s="38" t="inlineStr">
         <is>
           <t>无</t>
@@ -9704,7 +9786,11 @@
           <t>是</t>
         </is>
       </c>
-      <c r="Z40" s="38" t="n"/>
+      <c r="Z40" s="38" t="inlineStr">
+        <is>
+          <t>Active control</t>
+        </is>
+      </c>
       <c r="AA40" s="38" t="inlineStr">
         <is>
           <t>无</t>
@@ -9922,7 +10008,11 @@
           <t>是</t>
         </is>
       </c>
-      <c r="Z41" s="36" t="n"/>
+      <c r="Z41" s="36" t="inlineStr">
+        <is>
+          <t>Active control</t>
+        </is>
+      </c>
       <c r="AA41" s="36" t="inlineStr">
         <is>
           <t>无</t>
@@ -10358,7 +10448,11 @@
           <t>是</t>
         </is>
       </c>
-      <c r="Z43" s="36" t="n"/>
+      <c r="Z43" s="36" t="inlineStr">
+        <is>
+          <t>Active control</t>
+        </is>
+      </c>
       <c r="AA43" s="36" t="inlineStr">
         <is>
           <t>无</t>
@@ -10573,7 +10667,11 @@
           <t>是</t>
         </is>
       </c>
-      <c r="Z44" s="38" t="n"/>
+      <c r="Z44" s="38" t="inlineStr">
+        <is>
+          <t>Active control</t>
+        </is>
+      </c>
       <c r="AA44" s="38" t="inlineStr">
         <is>
           <t>无</t>
@@ -10796,7 +10894,11 @@
           <t>是</t>
         </is>
       </c>
-      <c r="Z45" s="36" t="n"/>
+      <c r="Z45" s="36" t="inlineStr">
+        <is>
+          <t>Active control</t>
+        </is>
+      </c>
       <c r="AA45" s="36" t="inlineStr">
         <is>
           <t>无</t>
@@ -11234,7 +11336,11 @@
           <t>是</t>
         </is>
       </c>
-      <c r="Z47" s="36" t="n"/>
+      <c r="Z47" s="36" t="inlineStr">
+        <is>
+          <t>Active control</t>
+        </is>
+      </c>
       <c r="AA47" s="36" t="inlineStr">
         <is>
           <t>无</t>
@@ -11450,7 +11556,11 @@
           <t>是</t>
         </is>
       </c>
-      <c r="Z48" s="38" t="n"/>
+      <c r="Z48" s="38" t="inlineStr">
+        <is>
+          <t>Active control</t>
+        </is>
+      </c>
       <c r="AA48" s="38" t="inlineStr">
         <is>
           <t>无</t>
@@ -11667,7 +11777,11 @@
           <t>是</t>
         </is>
       </c>
-      <c r="Z49" s="36" t="n"/>
+      <c r="Z49" s="36" t="inlineStr">
+        <is>
+          <t>Active control</t>
+        </is>
+      </c>
       <c r="AA49" s="36" t="inlineStr">
         <is>
           <t>无</t>
@@ -12315,7 +12429,11 @@
           <t>是</t>
         </is>
       </c>
-      <c r="Z52" s="38" t="n"/>
+      <c r="Z52" s="38" t="inlineStr">
+        <is>
+          <t>Active control</t>
+        </is>
+      </c>
       <c r="AA52" s="38" t="inlineStr">
         <is>
           <t>无</t>
@@ -12529,7 +12647,11 @@
           <t>是</t>
         </is>
       </c>
-      <c r="Z53" s="36" t="n"/>
+      <c r="Z53" s="36" t="inlineStr">
+        <is>
+          <t>Active control</t>
+        </is>
+      </c>
       <c r="AA53" s="36" t="inlineStr">
         <is>
           <t>无</t>
@@ -12758,7 +12880,11 @@
           <t>是</t>
         </is>
       </c>
-      <c r="Z54" s="38" t="n"/>
+      <c r="Z54" s="38" t="inlineStr">
+        <is>
+          <t>Active control</t>
+        </is>
+      </c>
       <c r="AA54" s="38" t="inlineStr">
         <is>
           <t>无</t>
@@ -13196,7 +13322,11 @@
           <t>是</t>
         </is>
       </c>
-      <c r="Z56" s="38" t="n"/>
+      <c r="Z56" s="38" t="inlineStr">
+        <is>
+          <t>Active control</t>
+        </is>
+      </c>
       <c r="AA56" s="38" t="inlineStr">
         <is>
           <t>无</t>
@@ -13423,7 +13553,11 @@
           <t>是</t>
         </is>
       </c>
-      <c r="Z57" s="36" t="n"/>
+      <c r="Z57" s="36" t="inlineStr">
+        <is>
+          <t>Active control</t>
+        </is>
+      </c>
       <c r="AA57" s="36" t="inlineStr">
         <is>
           <t>无</t>
@@ -13642,7 +13776,11 @@
           <t>是</t>
         </is>
       </c>
-      <c r="Z58" s="38" t="n"/>
+      <c r="Z58" s="38" t="inlineStr">
+        <is>
+          <t>Active control</t>
+        </is>
+      </c>
       <c r="AA58" s="38" t="inlineStr">
         <is>
           <t>无</t>

--- a/projects/paper-01/04-extract/数据_6_数据提取表_v3_xhs.xlsx
+++ b/projects/paper-01/04-extract/数据_6_数据提取表_v3_xhs.xlsx
@@ -1951,7 +1951,7 @@
       <c r="W5" s="35" t="n"/>
       <c r="X5" s="36" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>6</t>
         </is>
       </c>
       <c r="Y5" s="36" t="inlineStr">
@@ -2337,7 +2337,7 @@
       <c r="J7" s="36" t="n"/>
       <c r="K7" s="36" t="inlineStr">
         <is>
-          <t>25.44</t>
+          <t>84.22</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
@@ -2347,7 +2347,7 @@
       </c>
       <c r="M7" s="36" t="inlineStr">
         <is>
-          <t>3.32</t>
+          <t>11.33</t>
         </is>
       </c>
       <c r="N7" s="36" t="n">
@@ -4216,8 +4216,10 @@
         <v>60</v>
       </c>
       <c r="W15" s="35" t="n"/>
-      <c r="X15" s="36" t="n">
-        <v>1</v>
+      <c r="X15" s="36" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
       </c>
       <c r="Y15" s="36" t="inlineStr">
         <is>
@@ -4892,8 +4894,10 @@
         <v>45</v>
       </c>
       <c r="W18" s="37" t="n"/>
-      <c r="X18" s="38" t="n">
-        <v>4</v>
+      <c r="X18" s="38" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
       </c>
       <c r="Y18" s="38" t="inlineStr">
         <is>
@@ -5122,8 +5126,10 @@
         <v>60</v>
       </c>
       <c r="W19" s="35" t="n"/>
-      <c r="X19" s="36" t="n">
-        <v>2</v>
+      <c r="X19" s="36" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
       </c>
       <c r="Y19" s="36" t="inlineStr">
         <is>
@@ -5345,8 +5351,10 @@
         </is>
       </c>
       <c r="W20" s="37" t="n"/>
-      <c r="X20" s="38" t="n">
-        <v>5</v>
+      <c r="X20" s="38" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
       </c>
       <c r="Y20" s="38" t="inlineStr">
         <is>
@@ -5740,16 +5748,20 @@
       </c>
       <c r="I22" s="38" t="n"/>
       <c r="J22" s="38" t="n"/>
-      <c r="K22" s="38" t="n">
-        <v>71</v>
+      <c r="K22" s="38" t="inlineStr">
+        <is>
+          <t>12.84</t>
+        </is>
       </c>
       <c r="L22" t="inlineStr">
         <is>
           <t>young-old</t>
         </is>
       </c>
-      <c r="M22" s="38" t="n">
-        <v>4.6</v>
+      <c r="M22" s="38" t="inlineStr">
+        <is>
+          <t>89.07</t>
+        </is>
       </c>
       <c r="N22" s="38" t="n">
         <v>68</v>
@@ -5789,8 +5801,10 @@
         <v>45</v>
       </c>
       <c r="W22" s="37" t="n"/>
-      <c r="X22" s="38" t="n">
-        <v>12</v>
+      <c r="X22" s="38" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
       </c>
       <c r="Y22" s="38" t="inlineStr">
         <is>
@@ -7359,7 +7373,7 @@
       <c r="W29" s="35" t="n"/>
       <c r="X29" s="36" t="inlineStr">
         <is>
-          <t>2-4周</t>
+          <t>4</t>
         </is>
       </c>
       <c r="Y29" s="36" t="inlineStr">
@@ -7766,8 +7780,10 @@
       <c r="M31" s="36" t="n">
         <v>3.5</v>
       </c>
-      <c r="N31" s="36" t="n">
-        <v>57</v>
+      <c r="N31" s="36" t="inlineStr">
+        <is>
+          <t>65</t>
+        </is>
       </c>
       <c r="O31" s="36" t="n">
         <v>10.5</v>
@@ -7978,16 +7994,20 @@
       </c>
       <c r="I32" s="38" t="n"/>
       <c r="J32" s="38" t="n"/>
-      <c r="K32" s="38" t="n">
-        <v>69.7</v>
+      <c r="K32" s="38" t="inlineStr">
+        <is>
+          <t>48.82</t>
+        </is>
       </c>
       <c r="L32" t="inlineStr">
         <is>
           <t>young-old</t>
         </is>
       </c>
-      <c r="M32" s="38" t="n">
-        <v>4.5</v>
+      <c r="M32" s="38" t="inlineStr">
+        <is>
+          <t>10.66</t>
+        </is>
       </c>
       <c r="N32" s="38" t="n">
         <v>68</v>
@@ -8404,8 +8424,10 @@
       </c>
       <c r="I34" s="38" t="n"/>
       <c r="J34" s="38" t="n"/>
-      <c r="K34" s="38" t="n">
-        <v>83.5</v>
+      <c r="K34" s="38" t="inlineStr">
+        <is>
+          <t>84.1</t>
+        </is>
       </c>
       <c r="L34" t="inlineStr">
         <is>
@@ -8414,7 +8436,7 @@
       </c>
       <c r="M34" s="38" t="inlineStr">
         <is>
-          <t>未报告</t>
+          <t>69.7</t>
         </is>
       </c>
       <c r="N34" s="38" t="n">
@@ -8453,8 +8475,10 @@
         <v>45</v>
       </c>
       <c r="W34" s="37" t="n"/>
-      <c r="X34" s="38" t="n">
-        <v>14</v>
+      <c r="X34" s="38" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
       </c>
       <c r="Y34" s="38" t="inlineStr">
         <is>
@@ -8893,8 +8917,10 @@
         <v>45</v>
       </c>
       <c r="W36" s="37" t="n"/>
-      <c r="X36" s="38" t="n">
-        <v>12</v>
+      <c r="X36" s="38" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
       </c>
       <c r="Y36" s="38" t="inlineStr">
         <is>
@@ -9114,8 +9140,10 @@
       </c>
       <c r="V37" s="36" t="n"/>
       <c r="W37" s="35" t="n"/>
-      <c r="X37" s="36" t="n">
-        <v>6</v>
+      <c r="X37" s="36" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
       </c>
       <c r="Y37" s="36" t="inlineStr">
         <is>
@@ -10000,8 +10028,10 @@
         <v>40</v>
       </c>
       <c r="W41" s="35" t="n"/>
-      <c r="X41" s="36" t="n">
-        <v>5</v>
+      <c r="X41" s="36" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
       </c>
       <c r="Y41" s="36" t="inlineStr">
         <is>
@@ -10225,8 +10255,10 @@
         <v>30</v>
       </c>
       <c r="W42" s="37" t="n"/>
-      <c r="X42" s="38" t="n">
-        <v>5</v>
+      <c r="X42" s="38" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
       </c>
       <c r="Y42" s="38" t="inlineStr">
         <is>
@@ -10610,16 +10642,20 @@
       </c>
       <c r="I44" s="38" t="n"/>
       <c r="J44" s="38" t="n"/>
-      <c r="K44" s="38" t="n">
-        <v>69.40000000000001</v>
+      <c r="K44" s="38" t="inlineStr">
+        <is>
+          <t>49.68</t>
+        </is>
       </c>
       <c r="L44" t="inlineStr">
         <is>
           <t>young-old</t>
         </is>
       </c>
-      <c r="M44" s="38" t="n">
-        <v>2.89</v>
+      <c r="M44" s="38" t="inlineStr">
+        <is>
+          <t>73.24</t>
+        </is>
       </c>
       <c r="N44" s="38" t="n">
         <v>73</v>
@@ -10886,8 +10922,10 @@
         <v>30</v>
       </c>
       <c r="W45" s="35" t="n"/>
-      <c r="X45" s="36" t="n">
-        <v>8</v>
+      <c r="X45" s="36" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
       </c>
       <c r="Y45" s="36" t="inlineStr">
         <is>
@@ -11107,8 +11145,10 @@
         <v>28</v>
       </c>
       <c r="W46" s="37" t="n"/>
-      <c r="X46" s="38" t="n">
-        <v>2</v>
+      <c r="X46" s="38" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
       </c>
       <c r="Y46" s="38" t="inlineStr">
         <is>
@@ -11328,7 +11368,7 @@
       <c r="W47" s="35" t="n"/>
       <c r="X47" s="36" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>8</t>
         </is>
       </c>
       <c r="Y47" s="36" t="inlineStr">
@@ -11548,8 +11588,10 @@
         <v>30</v>
       </c>
       <c r="W48" s="37" t="n"/>
-      <c r="X48" s="38" t="n">
-        <v>5</v>
+      <c r="X48" s="38" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
       </c>
       <c r="Y48" s="38" t="inlineStr">
         <is>
@@ -11990,8 +12032,10 @@
         <v>30</v>
       </c>
       <c r="W50" s="37" t="n"/>
-      <c r="X50" s="38" t="n">
-        <v>1</v>
+      <c r="X50" s="38" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
       </c>
       <c r="Y50" s="38" t="inlineStr">
         <is>
@@ -12423,7 +12467,11 @@
         <v>60</v>
       </c>
       <c r="W52" s="37" t="n"/>
-      <c r="X52" s="38" t="n"/>
+      <c r="X52" s="38" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
       <c r="Y52" s="38" t="inlineStr">
         <is>
           <t>是</t>
@@ -12592,16 +12640,20 @@
       </c>
       <c r="I53" s="36" t="n"/>
       <c r="J53" s="36" t="n"/>
-      <c r="K53" s="36" t="n">
-        <v>69</v>
+      <c r="K53" s="36" t="inlineStr">
+        <is>
+          <t>51.08</t>
+        </is>
       </c>
       <c r="L53" t="inlineStr">
         <is>
           <t>young-old</t>
         </is>
       </c>
-      <c r="M53" s="36" t="n">
-        <v>3.5</v>
+      <c r="M53" s="36" t="inlineStr">
+        <is>
+          <t>11.35</t>
+        </is>
       </c>
       <c r="N53" s="36" t="n">
         <v>79</v>
@@ -12639,8 +12691,10 @@
         <v>30</v>
       </c>
       <c r="W53" s="35" t="n"/>
-      <c r="X53" s="36" t="n">
-        <v>3</v>
+      <c r="X53" s="36" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
       </c>
       <c r="Y53" s="36" t="inlineStr">
         <is>
@@ -12832,8 +12886,10 @@
       <c r="M54" s="38" t="n">
         <v>7.04</v>
       </c>
-      <c r="N54" s="38" t="n">
-        <v>48</v>
+      <c r="N54" s="38" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
       </c>
       <c r="O54" s="38" t="n">
         <v>13.33</v>
@@ -13545,8 +13601,10 @@
         <v>60</v>
       </c>
       <c r="W57" s="35" t="n"/>
-      <c r="X57" s="36" t="n">
-        <v>6</v>
+      <c r="X57" s="36" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="Y57" s="36" t="inlineStr">
         <is>

--- a/projects/paper-01/04-extract/数据_6_数据提取表_v3_xhs.xlsx
+++ b/projects/paper-01/04-extract/数据_6_数据提取表_v3_xhs.xlsx
@@ -3252,20 +3252,16 @@
       </c>
       <c r="I11" s="36" t="n"/>
       <c r="J11" s="36" t="n"/>
-      <c r="K11" s="36" t="inlineStr">
-        <is>
-          <t>5.92</t>
-        </is>
+      <c r="K11" s="36" t="n">
+        <v>69.5</v>
       </c>
       <c r="L11" t="inlineStr">
         <is>
           <t>young-old</t>
         </is>
       </c>
-      <c r="M11" s="36" t="inlineStr">
-        <is>
-          <t>41</t>
-        </is>
+      <c r="M11" s="36" t="n">
+        <v>5.2</v>
       </c>
       <c r="N11" s="36" t="n">
         <v>76</v>
@@ -3301,18 +3297,14 @@
         </is>
       </c>
       <c r="U11" s="36" t="n">
+        <v>11</v>
+      </c>
+      <c r="V11" s="36" t="n">
+        <v>20</v>
+      </c>
+      <c r="W11" s="35" t="n"/>
+      <c r="X11" s="36" t="n">
         <v>5</v>
-      </c>
-      <c r="V11" s="36" t="inlineStr">
-        <is>
-          <t>20+20</t>
-        </is>
-      </c>
-      <c r="W11" s="35" t="n"/>
-      <c r="X11" s="36" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
       </c>
       <c r="Y11" s="36" t="inlineStr">
         <is>
